--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время филиал на .xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время филиал на .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319AD221-62D7-4DA4-86E3-BEE6026DD6FE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6201A504-86B5-479B-BA92-8EE6D795A8E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -489,7 +489,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="221">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1146,6 +1146,12 @@
   </si>
   <si>
     <t>ПОСОЛЬСКАЯ ПМ с/к с/н в/у 1/100 10шт</t>
+  </si>
+  <si>
+    <t>ЭКСТРА Папа может вар п/о 0.4кг 8шт_195к</t>
+  </si>
+  <si>
+    <t>130439104 ООО "НОВОЕ ВРЕМЯ"  Мариуполь</t>
   </si>
 </sst>
 </file>
@@ -5663,7 +5669,12 @@
       </c>
     </row>
     <row r="4" spans="1:67" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="K4" s="132"/>
+      <c r="K4" s="132">
+        <v>130439104</v>
+      </c>
+      <c r="L4" s="128" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="5" spans="1:67" x14ac:dyDescent="0.25">
       <c r="C5" s="7" t="s">
@@ -6809,16 +6820,16 @@
     <row r="27" spans="1:67" s="62" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="57" t="str">
         <f t="shared" si="1"/>
-        <v>6353</v>
+        <v>7632</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>31</v>
+        <v>219</v>
       </c>
       <c r="C27" s="56" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="58">
-        <v>1001012506353</v>
+        <v>1001012507632</v>
       </c>
       <c r="E27" s="24"/>
       <c r="F27" s="59">

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время филиал на .xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время филиал на .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57AC3F00-E6D6-433A-8962-4C751D198375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75481470-8014-484B-8E1E-F74FF42ABC17}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,11 +17,19 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$162</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$598</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$598</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$164</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$600</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$600</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -481,7 +489,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="224">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1144,6 +1152,15 @@
   </si>
   <si>
     <t>130439104 ООО "НОВОЕ ВРЕМЯ"  Мариуполь</t>
+  </si>
+  <si>
+    <t>СЫРРРВЕЛАТ Папа может в/к в/у 0.28кг 8шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> БАВАРСКИЕ ПМ сос ц/о мгс 0.35кг 8шт.</t>
+  </si>
+  <si>
+    <t>САЛО СОЛЕНОЕ С ЧЕРНЫМ ПЕРЦЕМ мл/к в/у</t>
   </si>
 </sst>
 </file>
@@ -3162,6 +3179,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3982,6 +4029,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4292,136 +4359,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4482,6 +4419,56 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4582,6 +4569,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4692,11 +4689,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5177,9 +5194,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5217,9 +5234,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5252,9 +5269,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5287,9 +5321,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5466,7 +5517,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AX1686"/>
+  <dimension ref="A1:AX1688"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -6659,7 +6710,7 @@
         <v>6602</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="C38" s="50" t="s">
         <v>21</v>
@@ -7919,7 +7970,7 @@
     </row>
     <row r="81" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A81" s="55" t="str">
-        <f t="shared" ref="A81:A103" si="16">RIGHT(D81,4)</f>
+        <f t="shared" ref="A81:A104" si="16">RIGHT(D81,4)</f>
         <v>7564</v>
       </c>
       <c r="B81" s="53" t="s">
@@ -7968,7 +8019,7 @@
         <v>0.33</v>
       </c>
       <c r="G82" s="23">
-        <f t="shared" ref="G82:G92" si="17">E82*F82</f>
+        <f t="shared" ref="G82:G93" si="17">E82*F82</f>
         <v>0</v>
       </c>
       <c r="H82" s="14">
@@ -8254,87 +8305,83 @@
     <row r="92" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>6787</v>
-      </c>
-      <c r="B92" s="99" t="s">
-        <v>66</v>
+        <v>7489</v>
+      </c>
+      <c r="B92" s="53" t="s">
+        <v>221</v>
       </c>
       <c r="C92" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D92" s="51">
-        <v>1001300456787</v>
+        <v>1001307357489</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="23">
-        <v>0.33</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G92" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="G92" si="18">E92*F92</f>
         <v>0</v>
       </c>
-      <c r="H92" s="14">
-        <v>2.64</v>
-      </c>
-      <c r="I92" s="14">
-        <v>45</v>
-      </c>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
       <c r="J92" s="29"/>
     </row>
     <row r="93" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7166</v>
+        <v>6787</v>
       </c>
       <c r="B93" s="99" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D93" s="51">
-        <v>1001303987166</v>
+        <v>1001300456787</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="G93" s="23">
-        <f>E93</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H93" s="14">
-        <v>5.6</v>
+        <v>2.64</v>
       </c>
       <c r="I93" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J93" s="29"/>
     </row>
-    <row r="94" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7169</v>
-      </c>
-      <c r="B94" s="53" t="s">
-        <v>71</v>
+        <v>7166</v>
+      </c>
+      <c r="B94" s="99" t="s">
+        <v>72</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D94" s="51">
-        <v>1001303987169</v>
+        <v>1001303987166</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="G94" s="23">
-        <f>E94*F94</f>
+        <f>E94</f>
         <v>0</v>
       </c>
       <c r="H94" s="14">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="I94" s="14">
         <v>50</v>
@@ -8344,57 +8391,57 @@
     <row r="95" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>5544</v>
+        <v>7169</v>
       </c>
       <c r="B95" s="53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D95" s="51">
-        <v>1001051875544</v>
+        <v>1001303987169</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="23">
-        <v>0.81</v>
+        <v>0.35</v>
       </c>
       <c r="G95" s="23">
-        <f>E95</f>
+        <f>E95*F95</f>
         <v>0</v>
       </c>
       <c r="H95" s="14">
-        <v>4.8600000000000003</v>
+        <v>2.8</v>
       </c>
       <c r="I95" s="14">
-        <v>45</v>
-      </c>
-      <c r="J95" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="J95" s="29"/>
     </row>
     <row r="96" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>6697</v>
+        <v>5544</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D96" s="51">
-        <v>1001301876697</v>
+        <v>1001051875544</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.35</v>
+        <v>0.81</v>
       </c>
       <c r="G96" s="23">
-        <f t="shared" ref="G96:G103" si="18">E96*F96</f>
+        <f>E96</f>
         <v>0</v>
       </c>
       <c r="H96" s="14">
-        <v>2.8</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I96" s="14">
         <v>45</v>
@@ -8404,27 +8451,27 @@
     <row r="97" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7237</v>
+        <v>6697</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C97" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D97" s="51">
-        <v>1001304497237</v>
+        <v>1001301876697</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G97" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G97:G104" si="19">E97*F97</f>
         <v>0</v>
       </c>
       <c r="H97" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I97" s="14">
         <v>45</v>
@@ -8434,27 +8481,27 @@
     <row r="98" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7238</v>
+        <v>7237</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="C98" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D98" s="51">
-        <v>1001305197238</v>
+        <v>1001304497237</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="23">
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G98" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H98" s="14">
-        <v>2.48</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I98" s="14">
         <v>45</v>
@@ -8464,57 +8511,57 @@
     <row r="99" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7177</v>
+        <v>7238</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C99" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D99" s="51">
-        <v>1001302347177</v>
+        <v>1001305197238</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="23">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="G99" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H99" s="14">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="I99" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J99" s="49"/>
     </row>
     <row r="100" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7332</v>
+        <v>7177</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="C100" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D100" s="51">
-        <v>1001301777332</v>
+        <v>1001302347177</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G100" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H100" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I100" s="14">
         <v>50</v>
@@ -8524,23 +8571,23 @@
     <row r="101" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7333</v>
+        <v>7332</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C101" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D101" s="51">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="E101" s="24"/>
       <c r="F101" s="23">
         <v>0.28000000000000003</v>
       </c>
       <c r="G101" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H101" s="14">
@@ -8554,53 +8601,53 @@
     <row r="102" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>6459</v>
+        <v>7333</v>
       </c>
       <c r="B102" s="53" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C102" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D102" s="51">
-        <v>1001214196459</v>
+        <v>1001303987333</v>
       </c>
       <c r="E102" s="24"/>
       <c r="F102" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G102" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H102" s="14">
-        <v>1</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I102" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J102" s="49"/>
     </row>
-    <row r="103" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7474</v>
+        <v>6459</v>
       </c>
       <c r="B103" s="53" t="s">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="C103" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D103" s="51">
-        <v>1001216717474</v>
+        <v>1001214196459</v>
       </c>
       <c r="E103" s="24"/>
       <c r="F103" s="23">
         <v>0.1</v>
       </c>
       <c r="G103" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H103" s="14">
@@ -8611,76 +8658,76 @@
       </c>
       <c r="J103" s="49"/>
     </row>
-    <row r="104" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="47" t="s">
+    <row r="104" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="55" t="str">
+        <f t="shared" si="16"/>
+        <v>7474</v>
+      </c>
+      <c r="B104" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C104" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" s="51">
+        <v>1001216717474</v>
+      </c>
+      <c r="E104" s="24"/>
+      <c r="F104" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G104" s="23">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H104" s="14">
+        <v>1</v>
+      </c>
+      <c r="I104" s="14">
+        <v>45</v>
+      </c>
+      <c r="J104" s="49"/>
+    </row>
+    <row r="105" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B104" s="42" t="s">
+      <c r="B105" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C104" s="42"/>
-      <c r="D104" s="42"/>
-      <c r="E104" s="24"/>
-      <c r="F104" s="41"/>
-      <c r="G104" s="42"/>
-      <c r="H104" s="42"/>
-      <c r="I104" s="42"/>
-      <c r="J104" s="43"/>
-    </row>
-    <row r="105" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="55" t="str">
-        <f t="shared" ref="A105:A138" si="19">RIGHT(D105,4)</f>
+      <c r="C105" s="42"/>
+      <c r="D105" s="42"/>
+      <c r="E105" s="24"/>
+      <c r="F105" s="41"/>
+      <c r="G105" s="42"/>
+      <c r="H105" s="42"/>
+      <c r="I105" s="42"/>
+      <c r="J105" s="43"/>
+    </row>
+    <row r="106" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="55" t="str">
+        <f t="shared" ref="A106:A139" si="20">RIGHT(D106,4)</f>
         <v>3582</v>
       </c>
-      <c r="B105" s="53" t="s">
+      <c r="B106" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="C105" s="50" t="s">
+      <c r="C106" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D105" s="51">
+      <c r="D106" s="51">
         <v>1001061973582</v>
-      </c>
-      <c r="E105" s="24"/>
-      <c r="F105" s="56">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="G105" s="23">
-        <f>E105</f>
-        <v>0</v>
-      </c>
-      <c r="H105" s="94">
-        <v>3.9</v>
-      </c>
-      <c r="I105" s="93">
-        <v>120</v>
-      </c>
-      <c r="J105" s="29"/>
-    </row>
-    <row r="106" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>3986</v>
-      </c>
-      <c r="B106" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="C106" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D106" s="51">
-        <v>1001061973986</v>
       </c>
       <c r="E106" s="24"/>
       <c r="F106" s="56">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G106" s="23">
-        <f t="shared" ref="G106:G111" si="20">E106*F106</f>
+        <f>E106</f>
         <v>0</v>
       </c>
       <c r="H106" s="94">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I106" s="93">
         <v>120</v>
@@ -8689,58 +8736,58 @@
     </row>
     <row r="107" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>5931</v>
+        <f t="shared" si="20"/>
+        <v>3986</v>
       </c>
       <c r="B107" s="53" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C107" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D107" s="51">
-        <v>1001060755931</v>
+        <v>1001061973986</v>
       </c>
       <c r="E107" s="24"/>
-      <c r="F107" s="23">
-        <v>0.22</v>
+      <c r="F107" s="56">
+        <v>0.25</v>
       </c>
       <c r="G107" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G107:G112" si="21">E107*F107</f>
         <v>0</v>
       </c>
-      <c r="H107" s="92">
-        <v>1.76</v>
-      </c>
-      <c r="I107" s="14">
+      <c r="H107" s="94">
+        <v>2</v>
+      </c>
+      <c r="I107" s="93">
         <v>120</v>
       </c>
       <c r="J107" s="29"/>
     </row>
     <row r="108" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>5708</v>
+        <f t="shared" si="20"/>
+        <v>5931</v>
       </c>
       <c r="B108" s="53" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D108" s="51">
-        <v>1001063145708</v>
+        <v>1001060755931</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="23">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="G108" s="23">
-        <f t="shared" ref="G108:G109" si="21">E108</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H108" s="14">
-        <v>4</v>
+      <c r="H108" s="92">
+        <v>1.76</v>
       </c>
       <c r="I108" s="14">
         <v>120</v>
@@ -8749,28 +8796,28 @@
     </row>
     <row r="109" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>3287</v>
+        <f t="shared" si="20"/>
+        <v>5708</v>
       </c>
       <c r="B109" s="53" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C109" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D109" s="51">
-        <v>1001060763287</v>
+        <v>1001063145708</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="23">
-        <v>0.48799999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G109" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G109:G110" si="22">E109</f>
         <v>0</v>
       </c>
       <c r="H109" s="14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I109" s="14">
         <v>120</v>
@@ -8779,28 +8826,28 @@
     </row>
     <row r="110" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>4993</v>
+        <f t="shared" si="20"/>
+        <v>3287</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>204</v>
+        <v>91</v>
       </c>
       <c r="C110" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D110" s="51">
-        <v>1001060764993</v>
+        <v>1001060763287</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G110" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I110" s="14">
         <v>120</v>
@@ -8809,24 +8856,24 @@
     </row>
     <row r="111" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>5483</v>
+        <f t="shared" si="20"/>
+        <v>4993</v>
       </c>
       <c r="B111" s="53" t="s">
-        <v>89</v>
+        <v>204</v>
       </c>
       <c r="C111" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D111" s="51">
-        <v>1001062505483</v>
+        <v>1001060764993</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
         <v>0.25</v>
       </c>
       <c r="G111" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H111" s="14">
@@ -8839,28 +8886,28 @@
     </row>
     <row r="112" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>4117</v>
+        <f t="shared" si="20"/>
+        <v>5483</v>
       </c>
       <c r="B112" s="53" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C112" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D112" s="51">
-        <v>1001062504117</v>
+        <v>1001062505483</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G112" s="23">
-        <f t="shared" ref="G112:G113" si="22">E112</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H112" s="14">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="I112" s="14">
         <v>120</v>
@@ -8869,28 +8916,28 @@
     </row>
     <row r="113" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>0614</v>
+        <f t="shared" si="20"/>
+        <v>4117</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="C113" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D113" s="51">
-        <v>1001060720614</v>
+        <v>1001062504117</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
-        <v>0.52</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G113" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G113:G114" si="23">E113</f>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <v>3.64</v>
+        <v>3.95</v>
       </c>
       <c r="I113" s="14">
         <v>120</v>
@@ -8899,28 +8946,28 @@
     </row>
     <row r="114" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>6967</v>
+        <f t="shared" si="20"/>
+        <v>0614</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="C114" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D114" s="51">
-        <v>1001063656967</v>
+        <v>1001060720614</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="G114" s="23">
-        <f t="shared" ref="G114:G124" si="23">E114*F114</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="I114" s="14">
         <v>120</v>
@@ -8929,24 +8976,24 @@
     </row>
     <row r="115" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>6937</v>
+        <f t="shared" si="20"/>
+        <v>6967</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="C115" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D115" s="51">
-        <v>1001063106937</v>
+        <v>1001063656967</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
         <v>0.25</v>
       </c>
       <c r="G115" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G115:G125" si="24">E115*F115</f>
         <v>0</v>
       </c>
       <c r="H115" s="14">
@@ -8959,28 +9006,28 @@
     </row>
     <row r="116" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7143</v>
+        <f t="shared" si="20"/>
+        <v>6937</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C116" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D116" s="51">
-        <v>1001060717143</v>
+        <v>1001063106937</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H116" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I116" s="14">
         <v>120</v>
@@ -8989,24 +9036,24 @@
     </row>
     <row r="117" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7147</v>
+        <f t="shared" si="20"/>
+        <v>7143</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="C117" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D117" s="51">
-        <v>1001063237147</v>
+        <v>1001060717143</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
         <v>0.22</v>
       </c>
       <c r="G117" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H117" s="14">
@@ -9019,58 +9066,58 @@
     </row>
     <row r="118" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7456</v>
+        <f t="shared" si="20"/>
+        <v>7147</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>166</v>
+        <v>86</v>
       </c>
       <c r="C118" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D118" s="51">
-        <v>1001063097456</v>
+        <v>1001063237147</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G118" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I118" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J118" s="29"/>
     </row>
     <row r="119" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7364</v>
+        <f t="shared" si="20"/>
+        <v>7456</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D119" s="51">
-        <v>1001063217364</v>
+        <v>1001063097456</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G119" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I119" s="14">
         <v>90</v>
@@ -9079,24 +9126,24 @@
     </row>
     <row r="120" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7383</v>
+        <f t="shared" si="20"/>
+        <v>7364</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C120" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="51">
-        <v>1001065467383</v>
+        <v>1001063217364</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
         <v>0.22</v>
       </c>
       <c r="G120" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
@@ -9109,58 +9156,58 @@
     </row>
     <row r="121" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7317</v>
+        <f t="shared" si="20"/>
+        <v>7383</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C121" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D121" s="51">
-        <v>1001066567317</v>
+        <v>1001065467383</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G121" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H121" s="14">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I121" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J121" s="29"/>
     </row>
     <row r="122" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7318</v>
+        <f t="shared" si="20"/>
+        <v>7317</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C122" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D122" s="51">
-        <v>1001060727318</v>
+        <v>1001066567317</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G122" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
-        <v>2.16</v>
+        <v>3.78</v>
       </c>
       <c r="I122" s="14">
         <v>120</v>
@@ -9169,28 +9216,28 @@
     </row>
     <row r="123" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7316</v>
+        <f t="shared" si="20"/>
+        <v>7318</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C123" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D123" s="51">
-        <v>1001060727316</v>
+        <v>1001060727318</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="I123" s="14">
         <v>120</v>
@@ -9199,84 +9246,84 @@
     </row>
     <row r="124" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7417</v>
+        <f t="shared" si="20"/>
+        <v>7316</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C124" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D124" s="51">
-        <v>1001307147417</v>
+        <v>1001060727316</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="G124" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>1.76</v>
+        <v>3.78</v>
       </c>
       <c r="I124" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J124" s="29"/>
     </row>
     <row r="125" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>6832</v>
+        <f t="shared" si="20"/>
+        <v>7417</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="C125" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D125" s="51">
-        <v>1001065616832</v>
+        <v>1001307147417</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.215</v>
+        <v>0.44</v>
       </c>
       <c r="G125" s="23">
-        <f t="shared" ref="G125:G126" si="24">E125</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="I125" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="J125" s="29"/>
     </row>
     <row r="126" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7299</v>
+        <f t="shared" si="20"/>
+        <v>6832</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C126" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D126" s="51">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
         <v>0.215</v>
       </c>
       <c r="G126" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="G126:G127" si="25">E126</f>
         <v>0</v>
       </c>
       <c r="H126" s="14">
@@ -9289,84 +9336,84 @@
     </row>
     <row r="127" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7386</v>
+        <f t="shared" si="20"/>
+        <v>7299</v>
       </c>
       <c r="B127" s="53" t="s">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="C127" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D127" s="51">
-        <v>1001067017386</v>
+        <v>1001060677299</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="23">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G127" s="23">
-        <f t="shared" ref="G127:G137" si="25">E127*F127</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H127" s="14">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="I127" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J127" s="29"/>
     </row>
     <row r="128" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>6454</v>
+        <f t="shared" si="20"/>
+        <v>7386</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="C128" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D128" s="51">
-        <v>1001201976454</v>
+        <v>1001067017386</v>
       </c>
       <c r="E128" s="24"/>
       <c r="F128" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G128" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G128:G138" si="26">E128*F128</f>
         <v>0</v>
       </c>
       <c r="H128" s="14">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="I128" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J128" s="29"/>
     </row>
     <row r="129" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>6834</v>
+        <f t="shared" si="20"/>
+        <v>6454</v>
       </c>
       <c r="B129" s="53" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C129" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D129" s="51">
-        <v>1001203146834</v>
+        <v>1001201976454</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="23">
         <v>0.1</v>
       </c>
       <c r="G129" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H129" s="14">
@@ -9379,28 +9426,28 @@
     </row>
     <row r="130" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7382</v>
+        <f t="shared" si="20"/>
+        <v>6834</v>
       </c>
       <c r="B130" s="53" t="s">
-        <v>85</v>
+        <v>218</v>
       </c>
       <c r="C130" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D130" s="51">
-        <v>1001203117382</v>
+        <v>1001203146834</v>
       </c>
       <c r="E130" s="24"/>
       <c r="F130" s="23">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G130" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H130" s="14">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I130" s="14">
         <v>60</v>
@@ -9409,28 +9456,28 @@
     </row>
     <row r="131" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>6453</v>
+        <f t="shared" si="20"/>
+        <v>7382</v>
       </c>
       <c r="B131" s="53" t="s">
-        <v>208</v>
+        <v>85</v>
       </c>
       <c r="C131" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D131" s="51">
-        <v>1001202506453</v>
+        <v>1001203117382</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G131" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H131" s="14">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="I131" s="14">
         <v>60</v>
@@ -9439,28 +9486,28 @@
     </row>
     <row r="132" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>6221</v>
+        <f t="shared" si="20"/>
+        <v>6453</v>
       </c>
       <c r="B132" s="53" t="s">
-        <v>87</v>
+        <v>208</v>
       </c>
       <c r="C132" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D132" s="51">
-        <v>1001205376221</v>
+        <v>1001202506453</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G132" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H132" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I132" s="14">
         <v>60</v>
@@ -9469,24 +9516,24 @@
     </row>
     <row r="133" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>6222</v>
+        <f t="shared" si="20"/>
+        <v>6221</v>
       </c>
       <c r="B133" s="53" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="C133" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D133" s="51">
-        <v>1001205386222</v>
+        <v>1001205376221</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="23">
         <v>0.09</v>
       </c>
       <c r="G133" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H133" s="14">
@@ -9499,28 +9546,28 @@
     </row>
     <row r="134" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>6965</v>
+        <f t="shared" si="20"/>
+        <v>6222</v>
       </c>
       <c r="B134" s="53" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C134" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D134" s="51">
-        <v>1001206356965</v>
+        <v>1001205386222</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="23">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H134" s="14">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="I134" s="14">
         <v>60</v>
@@ -9529,28 +9576,28 @@
     </row>
     <row r="135" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>6557</v>
+        <f t="shared" si="20"/>
+        <v>6965</v>
       </c>
       <c r="B135" s="53" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C135" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D135" s="51">
-        <v>1001200756557</v>
+        <v>1001206356965</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="23">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G135" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H135" s="14">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="I135" s="14">
         <v>60</v>
@@ -9559,28 +9606,28 @@
     </row>
     <row r="136" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>5679</v>
+        <f t="shared" si="20"/>
+        <v>6557</v>
       </c>
       <c r="B136" s="53" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C136" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D136" s="51">
-        <v>1001190765679</v>
+        <v>1001200756557</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G136" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H136" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I136" s="14">
         <v>60</v>
@@ -9589,164 +9636,164 @@
     </row>
     <row r="137" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>5677</v>
+        <f t="shared" si="20"/>
+        <v>5679</v>
       </c>
       <c r="B137" s="53" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C137" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D137" s="51">
-        <v>1001190715677</v>
+        <v>1001190765679</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G137" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H137" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I137" s="14">
         <v>60</v>
       </c>
       <c r="J137" s="29"/>
     </row>
-    <row r="138" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v>7414</v>
+        <f t="shared" si="20"/>
+        <v>5677</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D138" s="51">
-        <v>1001204447414</v>
+        <v>1001190715677</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G138" s="23">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H138" s="14">
         <v>1</v>
-      </c>
-      <c r="G138" s="23">
-        <f>E138</f>
-        <v>0</v>
-      </c>
-      <c r="H138" s="14">
-        <v>8</v>
       </c>
       <c r="I138" s="14">
         <v>60</v>
       </c>
       <c r="J138" s="29"/>
     </row>
-    <row r="139" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="47" t="s">
+    <row r="139" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="55" t="str">
+        <f t="shared" si="20"/>
+        <v>7414</v>
+      </c>
+      <c r="B139" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="C139" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D139" s="51">
+        <v>1001204447414</v>
+      </c>
+      <c r="E139" s="24"/>
+      <c r="F139" s="23">
+        <v>1</v>
+      </c>
+      <c r="G139" s="23">
+        <f>E139</f>
+        <v>0</v>
+      </c>
+      <c r="H139" s="14">
+        <v>8</v>
+      </c>
+      <c r="I139" s="14">
+        <v>60</v>
+      </c>
+      <c r="J139" s="29"/>
+    </row>
+    <row r="140" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B139" s="42" t="s">
+      <c r="B140" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="C139" s="42"/>
-      <c r="D139" s="42"/>
-      <c r="E139" s="24"/>
-      <c r="F139" s="41"/>
-      <c r="G139" s="42"/>
-      <c r="H139" s="42"/>
-      <c r="I139" s="42"/>
-      <c r="J139" s="43"/>
-    </row>
-    <row r="140" spans="1:10" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="55" t="str">
-        <f t="shared" ref="A140:A149" si="26">RIGHT(D140,4)</f>
+      <c r="C140" s="42"/>
+      <c r="D140" s="42"/>
+      <c r="E140" s="24"/>
+      <c r="F140" s="41"/>
+      <c r="G140" s="42"/>
+      <c r="H140" s="42"/>
+      <c r="I140" s="42"/>
+      <c r="J140" s="43"/>
+    </row>
+    <row r="141" spans="1:10" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="55" t="str">
+        <f t="shared" ref="A141:A150" si="27">RIGHT(D141,4)</f>
         <v>4584</v>
       </c>
-      <c r="B140" s="98" t="s">
+      <c r="B141" s="98" t="s">
         <v>125</v>
       </c>
-      <c r="C140" s="50" t="s">
+      <c r="C141" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D140" s="97">
+      <c r="D141" s="97">
         <v>1001092674584</v>
       </c>
-      <c r="E140" s="24"/>
-      <c r="F140" s="23">
+      <c r="E141" s="24"/>
+      <c r="F141" s="23">
         <v>2.5</v>
       </c>
-      <c r="G140" s="23">
-        <f>E140</f>
+      <c r="G141" s="23">
+        <f>E141</f>
         <v>0</v>
       </c>
-      <c r="H140" s="14">
+      <c r="H141" s="14">
         <v>7.5</v>
       </c>
-      <c r="I140" s="14">
+      <c r="I141" s="14">
         <v>60</v>
-      </c>
-      <c r="J140" s="29"/>
-    </row>
-    <row r="141" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="55" t="str">
-        <f t="shared" si="26"/>
-        <v>6495</v>
-      </c>
-      <c r="B141" s="98" t="s">
-        <v>97</v>
-      </c>
-      <c r="C141" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D141" s="51">
-        <v>1001092436495</v>
-      </c>
-      <c r="E141" s="24"/>
-      <c r="F141" s="56">
-        <v>0.3</v>
-      </c>
-      <c r="G141" s="23">
-        <f>E141*F141</f>
-        <v>0</v>
-      </c>
-      <c r="H141" s="29">
-        <v>1.8</v>
-      </c>
-      <c r="I141" s="29">
-        <v>45</v>
       </c>
       <c r="J141" s="29"/>
     </row>
     <row r="142" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="55" t="str">
-        <f t="shared" si="26"/>
-        <v>6470</v>
-      </c>
-      <c r="B142" s="95" t="s">
-        <v>126</v>
+        <f t="shared" si="27"/>
+        <v>6495</v>
+      </c>
+      <c r="B142" s="98" t="s">
+        <v>97</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D142" s="51">
-        <v>1001092436470</v>
+        <v>1001092436495</v>
       </c>
       <c r="E142" s="24"/>
       <c r="F142" s="56">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G142" s="23">
-        <f t="shared" ref="G142:G143" si="27">E142</f>
+        <f>E142*F142</f>
         <v>0</v>
       </c>
       <c r="H142" s="29">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I142" s="29">
         <v>45</v>
@@ -9755,58 +9802,58 @@
     </row>
     <row r="143" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="55" t="str">
-        <f t="shared" si="26"/>
-        <v>5452</v>
+        <f t="shared" si="27"/>
+        <v>6470</v>
       </c>
       <c r="B143" s="95" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="C143" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D143" s="51">
-        <v>1001092485452</v>
+        <v>1001092436470</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="56">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="G143" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="G143:G144" si="28">E143</f>
         <v>0</v>
       </c>
       <c r="H143" s="29">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="I143" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J143" s="29"/>
     </row>
     <row r="144" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="55" t="str">
-        <f t="shared" si="26"/>
-        <v>3215</v>
+        <f t="shared" si="27"/>
+        <v>5452</v>
       </c>
       <c r="B144" s="95" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D144" s="51">
-        <v>1001094053215</v>
+        <v>1001092485452</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="56">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G144" s="23">
-        <f>E144*F144</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H144" s="29">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I144" s="29">
         <v>60</v>
@@ -9815,58 +9862,58 @@
     </row>
     <row r="145" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="55" t="str">
-        <f t="shared" si="26"/>
-        <v>6866</v>
+        <f t="shared" si="27"/>
+        <v>3215</v>
       </c>
       <c r="B145" s="95" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D145" s="51">
-        <v>1001095716866</v>
+        <v>1001094053215</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="56">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G145" s="23">
-        <f>E145</f>
+        <f>E145*F145</f>
         <v>0</v>
       </c>
       <c r="H145" s="29">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I145" s="29">
         <v>60</v>
       </c>
       <c r="J145" s="29"/>
     </row>
-    <row r="146" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="55" t="str">
-        <f t="shared" si="26"/>
-        <v>5495</v>
-      </c>
-      <c r="B146" s="53" t="s">
-        <v>96</v>
+        <f t="shared" si="27"/>
+        <v>6866</v>
+      </c>
+      <c r="B146" s="95" t="s">
+        <v>93</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D146" s="96">
-        <v>1001093345495</v>
+        <v>23</v>
+      </c>
+      <c r="D146" s="51">
+        <v>1001095716866</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="56">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G146" s="23">
-        <f t="shared" ref="G146:G148" si="28">E146*F146</f>
+        <f>E146</f>
         <v>0</v>
       </c>
       <c r="H146" s="29">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I146" s="29">
         <v>60</v>
@@ -9875,160 +9922,160 @@
     </row>
     <row r="147" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="55" t="str">
-        <f t="shared" si="26"/>
-        <v>7377</v>
+        <f t="shared" si="27"/>
+        <v>5495</v>
       </c>
       <c r="B147" s="53" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C147" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D147" s="96">
-        <v>1001095027377</v>
+        <v>1001093345495</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="56">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G147" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="G147:G149" si="29">E147*F147</f>
         <v>0</v>
       </c>
       <c r="H147" s="29">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I147" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J147" s="29"/>
     </row>
     <row r="148" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="55" t="str">
-        <f t="shared" si="26"/>
-        <v>6925</v>
+        <f t="shared" si="27"/>
+        <v>7377</v>
       </c>
       <c r="B148" s="53" t="s">
-        <v>214</v>
+        <v>127</v>
       </c>
       <c r="C148" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D148" s="96">
-        <v>1001095226925</v>
+        <v>1001095027377</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="56">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G148" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H148" s="29">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I148" s="29">
         <v>45</v>
       </c>
       <c r="J148" s="29"/>
     </row>
-    <row r="149" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="55" t="str">
-        <f t="shared" si="26"/>
-        <v>6025</v>
+        <f t="shared" si="27"/>
+        <v>6925</v>
       </c>
       <c r="B149" s="53" t="s">
-        <v>128</v>
+        <v>214</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D149" s="96">
-        <v>1001094966025</v>
+        <v>1001095226925</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="56">
+        <v>0.6</v>
+      </c>
+      <c r="G149" s="23">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H149" s="29">
+        <v>4.8</v>
+      </c>
+      <c r="I149" s="29">
+        <v>45</v>
+      </c>
+      <c r="J149" s="29"/>
+    </row>
+    <row r="150" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="55" t="str">
+        <f t="shared" si="27"/>
+        <v>6025</v>
+      </c>
+      <c r="B150" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C150" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D150" s="96">
+        <v>1001094966025</v>
+      </c>
+      <c r="E150" s="24"/>
+      <c r="F150" s="56">
         <v>3</v>
       </c>
-      <c r="G149" s="23">
-        <f>E149</f>
+      <c r="G150" s="23">
+        <f>E150</f>
         <v>0</v>
       </c>
-      <c r="H149" s="29">
+      <c r="H150" s="29">
         <v>6</v>
       </c>
-      <c r="I149" s="29">
+      <c r="I150" s="29">
         <v>60</v>
       </c>
-      <c r="J149" s="29"/>
-    </row>
-    <row r="150" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="47" t="s">
+      <c r="J150" s="29"/>
+    </row>
+    <row r="151" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B150" s="42" t="s">
+      <c r="B151" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="C150" s="42"/>
-      <c r="D150" s="42"/>
-      <c r="E150" s="24"/>
-      <c r="F150" s="41"/>
-      <c r="G150" s="42"/>
-      <c r="H150" s="42"/>
-      <c r="I150" s="42"/>
-      <c r="J150" s="43"/>
-    </row>
-    <row r="151" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="55" t="str">
-        <f t="shared" ref="A151:A161" si="29">RIGHT(D151,4)</f>
+      <c r="C151" s="42"/>
+      <c r="D151" s="42"/>
+      <c r="E151" s="24"/>
+      <c r="F151" s="41"/>
+      <c r="G151" s="42"/>
+      <c r="H151" s="42"/>
+      <c r="I151" s="42"/>
+      <c r="J151" s="43"/>
+    </row>
+    <row r="152" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="55" t="str">
+        <f t="shared" ref="A152:A163" si="30">RIGHT(D152,4)</f>
         <v>7090</v>
       </c>
-      <c r="B151" s="35" t="s">
+      <c r="B152" s="35" t="s">
         <v>102</v>
-      </c>
-      <c r="C151" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D151" s="51">
-        <v>1001084217090</v>
-      </c>
-      <c r="E151" s="24"/>
-      <c r="F151" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G151" s="23">
-        <f t="shared" ref="G151:G152" si="30">E151*F151</f>
-        <v>0</v>
-      </c>
-      <c r="H151" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I151" s="14">
-        <v>50</v>
-      </c>
-      <c r="J151" s="29"/>
-    </row>
-    <row r="152" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="55" t="str">
-        <f t="shared" si="29"/>
-        <v>7187</v>
-      </c>
-      <c r="B152" s="35" t="s">
-        <v>103</v>
       </c>
       <c r="C152" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D152" s="51">
-        <v>1001085637187</v>
+        <v>1001084217090</v>
       </c>
       <c r="E152" s="24"/>
       <c r="F152" s="23">
         <v>0.3</v>
       </c>
       <c r="G152" s="23">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="G152:G153" si="31">E152*F152</f>
         <v>0</v>
       </c>
       <c r="H152" s="14">
@@ -10041,178 +10088,172 @@
     </row>
     <row r="153" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="55" t="str">
-        <f t="shared" si="29"/>
-        <v>6620</v>
+        <f t="shared" si="30"/>
+        <v>7187</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C153" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D153" s="51">
-        <v>1001081596620</v>
+        <v>1001085637187</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G153" s="23">
-        <f>E153</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H153" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I153" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J153" s="29"/>
     </row>
     <row r="154" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="55" t="str">
-        <f t="shared" si="29"/>
-        <v>7103</v>
+        <f t="shared" si="30"/>
+        <v>6620</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D154" s="51">
-        <v>1001223297103</v>
+        <v>1001081596620</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
-        <v>0.18</v>
+        <v>1.05</v>
       </c>
       <c r="G154" s="23">
-        <f t="shared" ref="G154:G161" si="31">E154*F154</f>
+        <f>E154</f>
         <v>0</v>
       </c>
       <c r="H154" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I154" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J154" s="29"/>
     </row>
     <row r="155" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="55" t="str">
-        <f>RIGHT(D155,4)</f>
-        <v>7092</v>
+        <f t="shared" si="30"/>
+        <v>6008</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D155" s="51">
-        <v>1001223297092</v>
+        <v>1001084856008</v>
       </c>
       <c r="E155" s="24"/>
-      <c r="F155" s="23">
-        <v>0.14000000000000001</v>
-      </c>
+      <c r="F155" s="23"/>
       <c r="G155" s="23">
-        <f t="shared" si="31"/>
+        <f>E155</f>
         <v>0</v>
       </c>
-      <c r="H155" s="14">
-        <v>1.4</v>
-      </c>
-      <c r="I155" s="14">
-        <v>50</v>
-      </c>
+      <c r="H155" s="14"/>
+      <c r="I155" s="14"/>
       <c r="J155" s="29"/>
     </row>
     <row r="156" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="55" t="str">
-        <f t="shared" si="29"/>
-        <v>6228</v>
+        <f t="shared" si="30"/>
+        <v>7103</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C156" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D156" s="51">
-        <v>1001225416228</v>
+        <v>1001223297103</v>
       </c>
       <c r="E156" s="24"/>
       <c r="F156" s="23">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="G156" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="G156:G163" si="32">E156*F156</f>
         <v>0</v>
       </c>
       <c r="H156" s="14">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="I156" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J156" s="29"/>
     </row>
     <row r="157" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="55" t="str">
-        <f t="shared" si="29"/>
-        <v>6448</v>
+        <f>RIGHT(D157,4)</f>
+        <v>7092</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="C157" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D157" s="51">
-        <v>1001234146448</v>
+        <v>1001223297092</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G157" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I157" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J157" s="29"/>
     </row>
     <row r="158" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="55" t="str">
-        <f t="shared" si="29"/>
-        <v>6208</v>
+        <f t="shared" si="30"/>
+        <v>6228</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D158" s="51">
-        <v>1001220226208</v>
+        <v>1001225416228</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G158" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H158" s="14">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="I158" s="14">
         <v>45</v>
@@ -10221,135 +10262,175 @@
     </row>
     <row r="159" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="55" t="str">
-        <f t="shared" si="29"/>
-        <v>6754</v>
+        <f t="shared" si="30"/>
+        <v>6448</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D159" s="51">
-        <v>1001225406754</v>
+        <v>1001234146448</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G159" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H159" s="14">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="I159" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J159" s="29"/>
     </row>
     <row r="160" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="55" t="str">
-        <f t="shared" si="29"/>
-        <v>6279</v>
+        <f t="shared" si="30"/>
+        <v>6208</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C160" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D160" s="51">
-        <v>1001220286279</v>
+        <v>1001220226208</v>
       </c>
       <c r="E160" s="24"/>
       <c r="F160" s="23">
         <v>0.15</v>
       </c>
       <c r="G160" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H160" s="14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I160" s="14">
         <v>45</v>
       </c>
       <c r="J160" s="29"/>
     </row>
-    <row r="161" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="55" t="str">
-        <f t="shared" si="29"/>
-        <v>7288</v>
+        <f t="shared" si="30"/>
+        <v>6754</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
       <c r="C161" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D161" s="51">
-        <v>1001223907288</v>
+        <v>1001225406754</v>
       </c>
       <c r="E161" s="24"/>
       <c r="F161" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G161" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H161" s="14">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="I161" s="14">
         <v>60</v>
       </c>
       <c r="J161" s="29"/>
     </row>
-    <row r="162" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="48"/>
-      <c r="B162" s="45" t="s">
+    <row r="162" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="55" t="str">
+        <f t="shared" si="30"/>
+        <v>6279</v>
+      </c>
+      <c r="B162" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C162" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D162" s="51">
+        <v>1001220286279</v>
+      </c>
+      <c r="E162" s="24"/>
+      <c r="F162" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G162" s="23">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H162" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I162" s="14">
+        <v>45</v>
+      </c>
+      <c r="J162" s="29"/>
+    </row>
+    <row r="163" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="55" t="str">
+        <f t="shared" si="30"/>
+        <v>7288</v>
+      </c>
+      <c r="B163" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="C163" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D163" s="51">
+        <v>1001223907288</v>
+      </c>
+      <c r="E163" s="24"/>
+      <c r="F163" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G163" s="23">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H163" s="14">
+        <v>1</v>
+      </c>
+      <c r="I163" s="14">
+        <v>60</v>
+      </c>
+      <c r="J163" s="29"/>
+    </row>
+    <row r="164" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="48"/>
+      <c r="B164" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C162" s="16"/>
-      <c r="D162" s="36"/>
-      <c r="E162" s="17">
-        <f>SUM(E10:E161)</f>
+      <c r="C164" s="16"/>
+      <c r="D164" s="36"/>
+      <c r="E164" s="17">
+        <f>SUM(E10:E163)</f>
         <v>0</v>
       </c>
-      <c r="F162" s="17"/>
-      <c r="G162" s="17">
-        <f>SUM(G11:G161)</f>
+      <c r="F164" s="17"/>
+      <c r="G164" s="17">
+        <f>SUM(G11:G163)</f>
         <v>0</v>
       </c>
-      <c r="H162" s="17"/>
-      <c r="I162" s="17"/>
-      <c r="J162" s="17"/>
-    </row>
-    <row r="163" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="37"/>
-      <c r="C163" s="18"/>
-      <c r="D163" s="40"/>
-      <c r="F163" s="19"/>
-      <c r="G163" s="19"/>
-      <c r="H163" s="20"/>
-      <c r="I163" s="20"/>
-      <c r="J163" s="21"/>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B164" s="37"/>
-      <c r="C164" s="18"/>
-      <c r="D164" s="40"/>
-      <c r="F164" s="19"/>
-      <c r="G164" s="19"/>
-      <c r="H164" s="20"/>
-      <c r="I164" s="20"/>
-      <c r="J164" s="21"/>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H164" s="17"/>
+      <c r="I164" s="17"/>
+      <c r="J164" s="17"/>
+    </row>
+    <row r="165" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B165" s="37"/>
       <c r="C165" s="18"/>
       <c r="D165" s="40"/>
@@ -10412,11 +10493,10 @@
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B171" s="37"/>
       <c r="C171" s="18"/>
-      <c r="D171" s="53"/>
-      <c r="E171" s="4"/>
-      <c r="F171" s="53"/>
-      <c r="G171" s="57"/>
-      <c r="H171" s="51"/>
+      <c r="D171" s="40"/>
+      <c r="F171" s="19"/>
+      <c r="G171" s="19"/>
+      <c r="H171" s="20"/>
       <c r="I171" s="20"/>
       <c r="J171" s="21"/>
     </row>
@@ -10433,10 +10513,11 @@
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
       <c r="C173" s="18"/>
-      <c r="D173" s="40"/>
-      <c r="F173" s="19"/>
-      <c r="G173" s="19"/>
-      <c r="H173" s="20"/>
+      <c r="D173" s="53"/>
+      <c r="E173" s="4"/>
+      <c r="F173" s="53"/>
+      <c r="G173" s="57"/>
+      <c r="H173" s="51"/>
       <c r="I173" s="20"/>
       <c r="J173" s="21"/>
     </row>
@@ -25570,13 +25651,33 @@
       <c r="I1686" s="20"/>
       <c r="J1686" s="21"/>
     </row>
+    <row r="1687" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1687" s="37"/>
+      <c r="C1687" s="18"/>
+      <c r="D1687" s="40"/>
+      <c r="F1687" s="19"/>
+      <c r="G1687" s="19"/>
+      <c r="H1687" s="20"/>
+      <c r="I1687" s="20"/>
+      <c r="J1687" s="21"/>
+    </row>
+    <row r="1688" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1688" s="37"/>
+      <c r="C1688" s="18"/>
+      <c r="D1688" s="40"/>
+      <c r="F1688" s="19"/>
+      <c r="G1688" s="19"/>
+      <c r="H1688" s="20"/>
+      <c r="I1688" s="20"/>
+      <c r="J1688" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J162" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J164" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D171">
+  <conditionalFormatting sqref="D173">
     <cfRule type="duplicateValues" dxfId="312" priority="1"/>
     <cfRule type="duplicateValues" dxfId="311" priority="2"/>
     <cfRule type="duplicateValues" dxfId="310" priority="3"/>
@@ -28357,100 +28458,100 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="301" priority="307"/>
-    <cfRule type="duplicateValues" dxfId="300" priority="314"/>
-    <cfRule type="duplicateValues" dxfId="299" priority="313"/>
-    <cfRule type="duplicateValues" dxfId="298" priority="312"/>
-    <cfRule type="duplicateValues" dxfId="297" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="309"/>
     <cfRule type="duplicateValues" dxfId="296" priority="310"/>
-    <cfRule type="duplicateValues" dxfId="295" priority="309"/>
-    <cfRule type="duplicateValues" dxfId="294" priority="308"/>
-    <cfRule type="duplicateValues" dxfId="293" priority="306"/>
-    <cfRule type="duplicateValues" dxfId="292" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="314"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3">
-    <cfRule type="duplicateValues" dxfId="291" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="98"/>
     <cfRule type="duplicateValues" dxfId="290" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="289" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="288" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="287" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="286" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="285" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="284" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="283" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="282" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4">
     <cfRule type="duplicateValues" dxfId="281" priority="446"/>
-    <cfRule type="duplicateValues" dxfId="280" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="279" priority="451"/>
-    <cfRule type="duplicateValues" dxfId="278" priority="450"/>
-    <cfRule type="duplicateValues" dxfId="277" priority="449"/>
-    <cfRule type="duplicateValues" dxfId="276" priority="454"/>
-    <cfRule type="duplicateValues" dxfId="275" priority="448"/>
-    <cfRule type="duplicateValues" dxfId="274" priority="447"/>
-    <cfRule type="duplicateValues" dxfId="273" priority="453"/>
-    <cfRule type="duplicateValues" dxfId="272" priority="456"/>
-    <cfRule type="duplicateValues" dxfId="271" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="454"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="456"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B18">
     <cfRule type="duplicateValues" dxfId="270" priority="610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="269" priority="801"/>
-    <cfRule type="duplicateValues" dxfId="268" priority="807"/>
-    <cfRule type="duplicateValues" dxfId="267" priority="806"/>
-    <cfRule type="duplicateValues" dxfId="266" priority="805"/>
-    <cfRule type="duplicateValues" dxfId="265" priority="803"/>
-    <cfRule type="duplicateValues" dxfId="264" priority="802"/>
-    <cfRule type="duplicateValues" dxfId="263" priority="800"/>
-    <cfRule type="duplicateValues" dxfId="262" priority="804"/>
-    <cfRule type="duplicateValues" dxfId="261" priority="810"/>
-    <cfRule type="duplicateValues" dxfId="260" priority="808"/>
-    <cfRule type="duplicateValues" dxfId="259" priority="809"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="800"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="802"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="803"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="804"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="807"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="808"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="809"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="810"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="258" priority="705"/>
-    <cfRule type="duplicateValues" dxfId="257" priority="703"/>
-    <cfRule type="duplicateValues" dxfId="256" priority="701"/>
-    <cfRule type="duplicateValues" dxfId="255" priority="700"/>
-    <cfRule type="duplicateValues" dxfId="254" priority="708"/>
-    <cfRule type="duplicateValues" dxfId="253" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="700"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="701"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="703"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="704"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="705"/>
     <cfRule type="duplicateValues" dxfId="252" priority="706"/>
-    <cfRule type="duplicateValues" dxfId="251" priority="710"/>
-    <cfRule type="duplicateValues" dxfId="250" priority="709"/>
-    <cfRule type="duplicateValues" dxfId="249" priority="707"/>
-    <cfRule type="duplicateValues" dxfId="248" priority="704"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="707"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="708"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="710"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:B24">
     <cfRule type="duplicateValues" dxfId="247" priority="83"/>
     <cfRule type="duplicateValues" dxfId="246" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="245" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="244" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="243" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="242" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="88"/>
     <cfRule type="duplicateValues" dxfId="241" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="240" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="239" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="238" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="237" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="duplicateValues" dxfId="236" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="235" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="234" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="233" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="232" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="231" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="230" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="229" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27 B19 B21">
-    <cfRule type="duplicateValues" dxfId="228" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="245"/>
     <cfRule type="duplicateValues" dxfId="227" priority="246"/>
-    <cfRule type="duplicateValues" dxfId="226" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="247"/>
     <cfRule type="duplicateValues" dxfId="225" priority="248"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:B29">
@@ -28458,9 +28559,9 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
     <cfRule type="duplicateValues" dxfId="223" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="222" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="144"/>
     <cfRule type="duplicateValues" dxfId="221" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="220" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
     <cfRule type="duplicateValues" dxfId="219" priority="234"/>
@@ -28472,14 +28573,14 @@
     <cfRule type="duplicateValues" dxfId="217" priority="233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="216" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="215" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="214" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="213" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="212" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="211" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B40">
     <cfRule type="duplicateValues" dxfId="210" priority="190"/>
@@ -28488,16 +28589,16 @@
     <cfRule type="duplicateValues" dxfId="207" priority="193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41:B42">
-    <cfRule type="duplicateValues" dxfId="206" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="205" priority="260"/>
-    <cfRule type="duplicateValues" dxfId="204" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="203" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="202" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="201" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="200" priority="255"/>
-    <cfRule type="duplicateValues" dxfId="199" priority="256"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="197" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43 B39">
     <cfRule type="duplicateValues" dxfId="196" priority="231"/>
@@ -28506,33 +28607,33 @@
     <cfRule type="duplicateValues" dxfId="195" priority="232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="194" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="193" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="191" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="153"/>
     <cfRule type="duplicateValues" dxfId="188" priority="154"/>
     <cfRule type="duplicateValues" dxfId="187" priority="155"/>
     <cfRule type="duplicateValues" dxfId="186" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
     <cfRule type="duplicateValues" dxfId="185" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="140"/>
     <cfRule type="duplicateValues" dxfId="183" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="182" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="181" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="241"/>
     <cfRule type="duplicateValues" dxfId="180" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="243"/>
     <cfRule type="duplicateValues" dxfId="178" priority="244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="177" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="175" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
     <cfRule type="duplicateValues" dxfId="173" priority="176"/>
@@ -28547,10 +28648,10 @@
     <cfRule type="duplicateValues" dxfId="166" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="165" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56">
     <cfRule type="duplicateValues" dxfId="161" priority="168"/>
@@ -28559,22 +28660,22 @@
     <cfRule type="duplicateValues" dxfId="158" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57">
-    <cfRule type="duplicateValues" dxfId="157" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:B59 B44:B45 B55 B50:B51">
     <cfRule type="duplicateValues" dxfId="148" priority="294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="147" priority="239"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61:B62">
     <cfRule type="duplicateValues" dxfId="145" priority="290"/>
@@ -28604,37 +28705,37 @@
     <cfRule type="duplicateValues" dxfId="131" priority="230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="130" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="213"/>
     <cfRule type="duplicateValues" dxfId="129" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71:B72">
     <cfRule type="duplicateValues" dxfId="127" priority="228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73:B74 B70">
-    <cfRule type="duplicateValues" dxfId="126" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="262"/>
     <cfRule type="duplicateValues" dxfId="125" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="264"/>
     <cfRule type="duplicateValues" dxfId="123" priority="265"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="122" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76:B77">
-    <cfRule type="duplicateValues" dxfId="112" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B78">
     <cfRule type="duplicateValues" dxfId="107" priority="226"/>
@@ -28650,30 +28751,30 @@
     <cfRule type="duplicateValues" dxfId="103" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="102" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="121"/>
     <cfRule type="duplicateValues" dxfId="100" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88">
-    <cfRule type="duplicateValues" dxfId="98" priority="1037"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="1035"/>
     <cfRule type="duplicateValues" dxfId="97" priority="1036"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="1037"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B89">
-    <cfRule type="duplicateValues" dxfId="95" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="55"/>
     <cfRule type="duplicateValues" dxfId="94" priority="56"/>
     <cfRule type="duplicateValues" dxfId="93" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90">
     <cfRule type="duplicateValues" dxfId="91" priority="223"/>
     <cfRule type="duplicateValues" dxfId="90" priority="224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B91 B83:B84 B86:B87">
-    <cfRule type="duplicateValues" dxfId="89" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="285"/>
     <cfRule type="duplicateValues" dxfId="88" priority="286"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="287"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B91 B87">
     <cfRule type="duplicateValues" dxfId="86" priority="288"/>
@@ -28682,22 +28783,22 @@
     <cfRule type="duplicateValues" dxfId="85" priority="281"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99:B103">
-    <cfRule type="duplicateValues" dxfId="84" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="271"/>
     <cfRule type="duplicateValues" dxfId="81" priority="272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="80" priority="302"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="301"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="300"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="302"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105 B107:B110">
-    <cfRule type="duplicateValues" dxfId="76" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="276"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106">
     <cfRule type="duplicateValues" dxfId="72" priority="75"/>
@@ -28706,36 +28807,36 @@
     <cfRule type="duplicateValues" dxfId="69" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111:B113">
-    <cfRule type="duplicateValues" dxfId="68" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="72"/>
     <cfRule type="duplicateValues" dxfId="67" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="65" priority="222"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114:B116 B43:B45 B28:B30 B58:B60 B65:B66 B90 B78:B82 B32:B36 B92:B98 B55 B50:B51 B146:B151 B71:B72 B118 B128:B144 B5:B18 B68:B69 B120:B123 B38:B39">
-    <cfRule type="duplicateValues" dxfId="63" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115:B116">
     <cfRule type="duplicateValues" dxfId="61" priority="237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117">
-    <cfRule type="duplicateValues" dxfId="60" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118">
-    <cfRule type="duplicateValues" dxfId="51" priority="218"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119">
     <cfRule type="duplicateValues" dxfId="48" priority="42"/>
@@ -28748,30 +28849,30 @@
     <cfRule type="duplicateValues" dxfId="43" priority="268"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="42" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122:B123 B71:B72 B39 B43:B45 B114:B116 B28:B30 B58:B60 B65:B66 B78:B82 B90 B32:B36 B92:B98 B55 B50:B51 B128:B130 B5:B18 B68">
     <cfRule type="duplicateValues" dxfId="40" priority="289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B124:B125">
-    <cfRule type="duplicateValues" dxfId="39" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B126:B127">
     <cfRule type="duplicateValues" dxfId="35" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
     <cfRule type="duplicateValues" dxfId="33" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128:B130 B123">
     <cfRule type="duplicateValues" dxfId="31" priority="277"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B131">
-    <cfRule type="duplicateValues" dxfId="30" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132:B133">
     <cfRule type="duplicateValues" dxfId="28" priority="210"/>
@@ -28786,9 +28887,9 @@
     <cfRule type="duplicateValues" dxfId="25" priority="295"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B145">
-    <cfRule type="duplicateValues" dxfId="24" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
     <cfRule type="duplicateValues" dxfId="21" priority="212"/>
@@ -28803,9 +28904,9 @@
     <cfRule type="duplicateValues" dxfId="18" priority="296"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="17" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="278"/>
     <cfRule type="duplicateValues" dxfId="16" priority="279"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="280"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
     <cfRule type="duplicateValues" dxfId="14" priority="68"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время филиал на .xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время филиал на .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75481470-8014-484B-8E1E-F74FF42ABC17}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C2386E-81D3-4AF7-8FD4-4288D58776DE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$164</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$600</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$600</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$165</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$601</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$601</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -489,7 +489,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="225">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1161,6 +1161,9 @@
   </si>
   <si>
     <t>САЛО СОЛЕНОЕ С ЧЕРНЫМ ПЕРЦЕМ мл/к в/у</t>
+  </si>
+  <si>
+    <t>НАБОР ДЛЯ ПИЦЦЫ с/к с/н мгс 3*3_HRC</t>
   </si>
 </sst>
 </file>
@@ -5517,7 +5520,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AX1688"/>
+  <dimension ref="A1:AX1689"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -5571,14 +5574,14 @@
         <v>2</v>
       </c>
       <c r="D3" s="54">
-        <v>46194</v>
+        <v>46209</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="54">
         <f>D3+3</f>
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="G3" s="105" t="s">
         <v>203</v>
@@ -8706,7 +8709,7 @@
     </row>
     <row r="106" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A106" s="55" t="str">
-        <f t="shared" ref="A106:A139" si="20">RIGHT(D106,4)</f>
+        <f t="shared" ref="A106:A140" si="20">RIGHT(D106,4)</f>
         <v>3582</v>
       </c>
       <c r="B106" s="53" t="s">
@@ -9323,7 +9326,7 @@
         <v>0.215</v>
       </c>
       <c r="G126" s="23">
-        <f t="shared" ref="G126:G127" si="25">E126</f>
+        <f t="shared" ref="G126:G128" si="25">E126</f>
         <v>0</v>
       </c>
       <c r="H126" s="14">
@@ -9367,76 +9370,70 @@
     <row r="128" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7386</v>
+        <v>7442</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C128" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D128" s="51">
-        <v>1001067017386</v>
+        <v>1001200677442</v>
       </c>
       <c r="E128" s="24"/>
-      <c r="F128" s="23">
-        <v>0.15</v>
-      </c>
+      <c r="F128" s="23"/>
       <c r="G128" s="23">
-        <f t="shared" ref="G128:G138" si="26">E128*F128</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="H128" s="14">
-        <v>1.35</v>
-      </c>
-      <c r="I128" s="14">
-        <v>90</v>
-      </c>
+      <c r="H128" s="14"/>
+      <c r="I128" s="14"/>
       <c r="J128" s="29"/>
     </row>
     <row r="129" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6454</v>
+        <v>7386</v>
       </c>
       <c r="B129" s="53" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="C129" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D129" s="51">
-        <v>1001201976454</v>
+        <v>1001067017386</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G129" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="G129:G139" si="26">E129*F129</f>
         <v>0</v>
       </c>
       <c r="H129" s="14">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="I129" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J129" s="29"/>
     </row>
     <row r="130" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6834</v>
+        <v>6454</v>
       </c>
       <c r="B130" s="53" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C130" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D130" s="51">
-        <v>1001203146834</v>
+        <v>1001201976454</v>
       </c>
       <c r="E130" s="24"/>
       <c r="F130" s="23">
@@ -9457,27 +9454,27 @@
     <row r="131" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7382</v>
+        <v>6834</v>
       </c>
       <c r="B131" s="53" t="s">
-        <v>85</v>
+        <v>218</v>
       </c>
       <c r="C131" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D131" s="51">
-        <v>1001203117382</v>
+        <v>1001203146834</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="23">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G131" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H131" s="14">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I131" s="14">
         <v>60</v>
@@ -9487,27 +9484,27 @@
     <row r="132" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6453</v>
+        <v>7382</v>
       </c>
       <c r="B132" s="53" t="s">
-        <v>208</v>
+        <v>85</v>
       </c>
       <c r="C132" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D132" s="51">
-        <v>1001202506453</v>
+        <v>1001203117382</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G132" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H132" s="14">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="I132" s="14">
         <v>60</v>
@@ -9517,27 +9514,27 @@
     <row r="133" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6221</v>
+        <v>6453</v>
       </c>
       <c r="B133" s="53" t="s">
-        <v>87</v>
+        <v>208</v>
       </c>
       <c r="C133" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D133" s="51">
-        <v>1001205376221</v>
+        <v>1001202506453</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G133" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H133" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I133" s="14">
         <v>60</v>
@@ -9547,16 +9544,16 @@
     <row r="134" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6222</v>
+        <v>6221</v>
       </c>
       <c r="B134" s="53" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="C134" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D134" s="51">
-        <v>1001205386222</v>
+        <v>1001205376221</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="23">
@@ -9577,27 +9574,27 @@
     <row r="135" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6965</v>
+        <v>6222</v>
       </c>
       <c r="B135" s="53" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C135" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D135" s="51">
-        <v>1001206356965</v>
+        <v>1001205386222</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="23">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="G135" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H135" s="14">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="I135" s="14">
         <v>60</v>
@@ -9607,27 +9604,27 @@
     <row r="136" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6557</v>
+        <v>6965</v>
       </c>
       <c r="B136" s="53" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C136" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D136" s="51">
-        <v>1001200756557</v>
+        <v>1001206356965</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="23">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G136" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H136" s="14">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="I136" s="14">
         <v>60</v>
@@ -9637,27 +9634,27 @@
     <row r="137" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>5679</v>
+        <v>6557</v>
       </c>
       <c r="B137" s="53" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C137" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D137" s="51">
-        <v>1001190765679</v>
+        <v>1001200756557</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G137" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H137" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I137" s="14">
         <v>60</v>
@@ -9667,163 +9664,163 @@
     <row r="138" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>5677</v>
+        <v>5679</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C138" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D138" s="51">
-        <v>1001190715677</v>
+        <v>1001190765679</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G138" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H138" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I138" s="14">
         <v>60</v>
       </c>
       <c r="J138" s="29"/>
     </row>
-    <row r="139" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7414</v>
+        <v>5677</v>
       </c>
       <c r="B139" s="53" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D139" s="51">
-        <v>1001204447414</v>
+        <v>1001190715677</v>
       </c>
       <c r="E139" s="24"/>
       <c r="F139" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G139" s="23">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H139" s="14">
         <v>1</v>
-      </c>
-      <c r="G139" s="23">
-        <f>E139</f>
-        <v>0</v>
-      </c>
-      <c r="H139" s="14">
-        <v>8</v>
       </c>
       <c r="I139" s="14">
         <v>60</v>
       </c>
       <c r="J139" s="29"/>
     </row>
-    <row r="140" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="47" t="s">
+    <row r="140" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="55" t="str">
+        <f t="shared" si="20"/>
+        <v>7414</v>
+      </c>
+      <c r="B140" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="C140" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D140" s="51">
+        <v>1001204447414</v>
+      </c>
+      <c r="E140" s="24"/>
+      <c r="F140" s="23">
+        <v>1</v>
+      </c>
+      <c r="G140" s="23">
+        <f>E140</f>
+        <v>0</v>
+      </c>
+      <c r="H140" s="14">
+        <v>8</v>
+      </c>
+      <c r="I140" s="14">
+        <v>60</v>
+      </c>
+      <c r="J140" s="29"/>
+    </row>
+    <row r="141" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B140" s="42" t="s">
+      <c r="B141" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="C140" s="42"/>
-      <c r="D140" s="42"/>
-      <c r="E140" s="24"/>
-      <c r="F140" s="41"/>
-      <c r="G140" s="42"/>
-      <c r="H140" s="42"/>
-      <c r="I140" s="42"/>
-      <c r="J140" s="43"/>
-    </row>
-    <row r="141" spans="1:10" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="55" t="str">
-        <f t="shared" ref="A141:A150" si="27">RIGHT(D141,4)</f>
+      <c r="C141" s="42"/>
+      <c r="D141" s="42"/>
+      <c r="E141" s="24"/>
+      <c r="F141" s="41"/>
+      <c r="G141" s="42"/>
+      <c r="H141" s="42"/>
+      <c r="I141" s="42"/>
+      <c r="J141" s="43"/>
+    </row>
+    <row r="142" spans="1:10" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="55" t="str">
+        <f t="shared" ref="A142:A151" si="27">RIGHT(D142,4)</f>
         <v>4584</v>
       </c>
-      <c r="B141" s="98" t="s">
+      <c r="B142" s="98" t="s">
         <v>125</v>
       </c>
-      <c r="C141" s="50" t="s">
+      <c r="C142" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D141" s="97">
+      <c r="D142" s="97">
         <v>1001092674584</v>
       </c>
-      <c r="E141" s="24"/>
-      <c r="F141" s="23">
+      <c r="E142" s="24"/>
+      <c r="F142" s="23">
         <v>2.5</v>
       </c>
-      <c r="G141" s="23">
-        <f>E141</f>
+      <c r="G142" s="23">
+        <f>E142</f>
         <v>0</v>
       </c>
-      <c r="H141" s="14">
+      <c r="H142" s="14">
         <v>7.5</v>
       </c>
-      <c r="I141" s="14">
+      <c r="I142" s="14">
         <v>60</v>
-      </c>
-      <c r="J141" s="29"/>
-    </row>
-    <row r="142" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="55" t="str">
-        <f t="shared" si="27"/>
-        <v>6495</v>
-      </c>
-      <c r="B142" s="98" t="s">
-        <v>97</v>
-      </c>
-      <c r="C142" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D142" s="51">
-        <v>1001092436495</v>
-      </c>
-      <c r="E142" s="24"/>
-      <c r="F142" s="56">
-        <v>0.3</v>
-      </c>
-      <c r="G142" s="23">
-        <f>E142*F142</f>
-        <v>0</v>
-      </c>
-      <c r="H142" s="29">
-        <v>1.8</v>
-      </c>
-      <c r="I142" s="29">
-        <v>45</v>
       </c>
       <c r="J142" s="29"/>
     </row>
     <row r="143" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>6470</v>
-      </c>
-      <c r="B143" s="95" t="s">
-        <v>126</v>
+        <v>6495</v>
+      </c>
+      <c r="B143" s="98" t="s">
+        <v>97</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D143" s="51">
-        <v>1001092436470</v>
+        <v>1001092436495</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="56">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G143" s="23">
-        <f t="shared" ref="G143:G144" si="28">E143</f>
+        <f>E143*F143</f>
         <v>0</v>
       </c>
       <c r="H143" s="29">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I143" s="29">
         <v>45</v>
@@ -9833,57 +9830,57 @@
     <row r="144" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>5452</v>
+        <v>6470</v>
       </c>
       <c r="B144" s="95" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="C144" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D144" s="51">
-        <v>1001092485452</v>
+        <v>1001092436470</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="56">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="G144" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="G144:G145" si="28">E144</f>
         <v>0</v>
       </c>
       <c r="H144" s="29">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="I144" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J144" s="29"/>
     </row>
     <row r="145" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>3215</v>
+        <v>5452</v>
       </c>
       <c r="B145" s="95" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D145" s="51">
-        <v>1001094053215</v>
+        <v>1001092485452</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="56">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G145" s="23">
-        <f>E145*F145</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H145" s="29">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I145" s="29">
         <v>60</v>
@@ -9893,57 +9890,57 @@
     <row r="146" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>6866</v>
+        <v>3215</v>
       </c>
       <c r="B146" s="95" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D146" s="51">
-        <v>1001095716866</v>
+        <v>1001094053215</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="56">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G146" s="23">
-        <f>E146</f>
+        <f>E146*F146</f>
         <v>0</v>
       </c>
       <c r="H146" s="29">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I146" s="29">
         <v>60</v>
       </c>
       <c r="J146" s="29"/>
     </row>
-    <row r="147" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>5495</v>
-      </c>
-      <c r="B147" s="53" t="s">
-        <v>96</v>
+        <v>6866</v>
+      </c>
+      <c r="B147" s="95" t="s">
+        <v>93</v>
       </c>
       <c r="C147" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D147" s="96">
-        <v>1001093345495</v>
+        <v>23</v>
+      </c>
+      <c r="D147" s="51">
+        <v>1001095716866</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="56">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G147" s="23">
-        <f t="shared" ref="G147:G149" si="29">E147*F147</f>
+        <f>E147</f>
         <v>0</v>
       </c>
       <c r="H147" s="29">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I147" s="29">
         <v>60</v>
@@ -9953,159 +9950,159 @@
     <row r="148" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>7377</v>
+        <v>5495</v>
       </c>
       <c r="B148" s="53" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C148" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D148" s="96">
-        <v>1001095027377</v>
+        <v>1001093345495</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="56">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G148" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="G148:G150" si="29">E148*F148</f>
         <v>0</v>
       </c>
       <c r="H148" s="29">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I148" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J148" s="29"/>
     </row>
     <row r="149" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>6925</v>
+        <v>7377</v>
       </c>
       <c r="B149" s="53" t="s">
-        <v>214</v>
+        <v>127</v>
       </c>
       <c r="C149" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D149" s="96">
-        <v>1001095226925</v>
+        <v>1001095027377</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="56">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G149" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H149" s="29">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I149" s="29">
         <v>45</v>
       </c>
       <c r="J149" s="29"/>
     </row>
-    <row r="150" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>6025</v>
+        <v>6925</v>
       </c>
       <c r="B150" s="53" t="s">
-        <v>128</v>
+        <v>214</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D150" s="96">
-        <v>1001094966025</v>
+        <v>1001095226925</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="56">
+        <v>0.6</v>
+      </c>
+      <c r="G150" s="23">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H150" s="29">
+        <v>4.8</v>
+      </c>
+      <c r="I150" s="29">
+        <v>45</v>
+      </c>
+      <c r="J150" s="29"/>
+    </row>
+    <row r="151" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="55" t="str">
+        <f t="shared" si="27"/>
+        <v>6025</v>
+      </c>
+      <c r="B151" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C151" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D151" s="96">
+        <v>1001094966025</v>
+      </c>
+      <c r="E151" s="24"/>
+      <c r="F151" s="56">
         <v>3</v>
       </c>
-      <c r="G150" s="23">
-        <f>E150</f>
+      <c r="G151" s="23">
+        <f>E151</f>
         <v>0</v>
       </c>
-      <c r="H150" s="29">
+      <c r="H151" s="29">
         <v>6</v>
       </c>
-      <c r="I150" s="29">
+      <c r="I151" s="29">
         <v>60</v>
       </c>
-      <c r="J150" s="29"/>
-    </row>
-    <row r="151" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="47" t="s">
+      <c r="J151" s="29"/>
+    </row>
+    <row r="152" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B151" s="42" t="s">
+      <c r="B152" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="C151" s="42"/>
-      <c r="D151" s="42"/>
-      <c r="E151" s="24"/>
-      <c r="F151" s="41"/>
-      <c r="G151" s="42"/>
-      <c r="H151" s="42"/>
-      <c r="I151" s="42"/>
-      <c r="J151" s="43"/>
-    </row>
-    <row r="152" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="55" t="str">
-        <f t="shared" ref="A152:A163" si="30">RIGHT(D152,4)</f>
+      <c r="C152" s="42"/>
+      <c r="D152" s="42"/>
+      <c r="E152" s="24"/>
+      <c r="F152" s="41"/>
+      <c r="G152" s="42"/>
+      <c r="H152" s="42"/>
+      <c r="I152" s="42"/>
+      <c r="J152" s="43"/>
+    </row>
+    <row r="153" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="55" t="str">
+        <f t="shared" ref="A153:A164" si="30">RIGHT(D153,4)</f>
         <v>7090</v>
       </c>
-      <c r="B152" s="35" t="s">
+      <c r="B153" s="35" t="s">
         <v>102</v>
-      </c>
-      <c r="C152" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D152" s="51">
-        <v>1001084217090</v>
-      </c>
-      <c r="E152" s="24"/>
-      <c r="F152" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G152" s="23">
-        <f t="shared" ref="G152:G153" si="31">E152*F152</f>
-        <v>0</v>
-      </c>
-      <c r="H152" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I152" s="14">
-        <v>50</v>
-      </c>
-      <c r="J152" s="29"/>
-    </row>
-    <row r="153" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="55" t="str">
-        <f t="shared" si="30"/>
-        <v>7187</v>
-      </c>
-      <c r="B153" s="35" t="s">
-        <v>103</v>
       </c>
       <c r="C153" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D153" s="51">
-        <v>1001085637187</v>
+        <v>1001084217090</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="23">
         <v>0.3</v>
       </c>
       <c r="G153" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="G153:G154" si="31">E153*F153</f>
         <v>0</v>
       </c>
       <c r="H153" s="14">
@@ -10119,111 +10116,111 @@
     <row r="154" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6620</v>
+        <v>7187</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D154" s="51">
-        <v>1001081596620</v>
+        <v>1001085637187</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G154" s="23">
-        <f>E154</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H154" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I154" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J154" s="29"/>
     </row>
     <row r="155" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6008</v>
+        <v>6620</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>223</v>
+        <v>99</v>
       </c>
       <c r="C155" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D155" s="51">
-        <v>1001084856008</v>
+        <v>1001081596620</v>
       </c>
       <c r="E155" s="24"/>
-      <c r="F155" s="23"/>
+      <c r="F155" s="23">
+        <v>1.05</v>
+      </c>
       <c r="G155" s="23">
         <f>E155</f>
         <v>0</v>
       </c>
-      <c r="H155" s="14"/>
-      <c r="I155" s="14"/>
+      <c r="H155" s="14">
+        <v>3.15</v>
+      </c>
+      <c r="I155" s="14">
+        <v>30</v>
+      </c>
       <c r="J155" s="29"/>
     </row>
     <row r="156" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>7103</v>
+        <v>6008</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>104</v>
+        <v>223</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D156" s="51">
-        <v>1001223297103</v>
+        <v>1001084856008</v>
       </c>
       <c r="E156" s="24"/>
-      <c r="F156" s="23">
-        <v>0.18</v>
-      </c>
+      <c r="F156" s="23"/>
       <c r="G156" s="23">
-        <f t="shared" ref="G156:G163" si="32">E156*F156</f>
+        <f>E156</f>
         <v>0</v>
       </c>
-      <c r="H156" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I156" s="14">
-        <v>50</v>
-      </c>
+      <c r="H156" s="14"/>
+      <c r="I156" s="14"/>
       <c r="J156" s="29"/>
     </row>
     <row r="157" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="55" t="str">
-        <f>RIGHT(D157,4)</f>
-        <v>7092</v>
+        <f t="shared" si="30"/>
+        <v>7103</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C157" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D157" s="51">
-        <v>1001223297092</v>
+        <v>1001223297103</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G157" s="23">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="G157:G164" si="32">E157*F157</f>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I157" s="14">
         <v>50</v>
@@ -10232,58 +10229,58 @@
     </row>
     <row r="158" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="55" t="str">
-        <f t="shared" si="30"/>
-        <v>6228</v>
+        <f>RIGHT(D158,4)</f>
+        <v>7092</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D158" s="51">
-        <v>1001225416228</v>
+        <v>1001223297092</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G158" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H158" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I158" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J158" s="29"/>
     </row>
     <row r="159" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6448</v>
+        <v>6228</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D159" s="51">
-        <v>1001234146448</v>
+        <v>1001225416228</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G159" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H159" s="14">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I159" s="14">
         <v>45</v>
@@ -10293,27 +10290,27 @@
     <row r="160" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6208</v>
+        <v>6448</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C160" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D160" s="51">
-        <v>1001220226208</v>
+        <v>1001234146448</v>
       </c>
       <c r="E160" s="24"/>
       <c r="F160" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G160" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H160" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I160" s="14">
         <v>45</v>
@@ -10323,124 +10320,144 @@
     <row r="161" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6754</v>
+        <v>6208</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="C161" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D161" s="51">
-        <v>1001225406754</v>
+        <v>1001220226208</v>
       </c>
       <c r="E161" s="24"/>
       <c r="F161" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G161" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H161" s="14">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="I161" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J161" s="29"/>
     </row>
     <row r="162" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6279</v>
+        <v>6754</v>
       </c>
       <c r="B162" s="35" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C162" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D162" s="51">
-        <v>1001220286279</v>
+        <v>1001225406754</v>
       </c>
       <c r="E162" s="24"/>
       <c r="F162" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G162" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H162" s="14">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="I162" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J162" s="29"/>
     </row>
-    <row r="163" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>7288</v>
+        <v>6279</v>
       </c>
       <c r="B163" s="35" t="s">
-        <v>213</v>
+        <v>100</v>
       </c>
       <c r="C163" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D163" s="51">
-        <v>1001223907288</v>
+        <v>1001220286279</v>
       </c>
       <c r="E163" s="24"/>
       <c r="F163" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G163" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H163" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I163" s="14">
+        <v>45</v>
+      </c>
+      <c r="J163" s="29"/>
+    </row>
+    <row r="164" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="55" t="str">
+        <f t="shared" si="30"/>
+        <v>7288</v>
+      </c>
+      <c r="B164" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="C164" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D164" s="51">
+        <v>1001223907288</v>
+      </c>
+      <c r="E164" s="24"/>
+      <c r="F164" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G164" s="23">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H164" s="14">
         <v>1</v>
       </c>
-      <c r="I163" s="14">
+      <c r="I164" s="14">
         <v>60</v>
       </c>
-      <c r="J163" s="29"/>
-    </row>
-    <row r="164" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="48"/>
-      <c r="B164" s="45" t="s">
+      <c r="J164" s="29"/>
+    </row>
+    <row r="165" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="48"/>
+      <c r="B165" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C164" s="16"/>
-      <c r="D164" s="36"/>
-      <c r="E164" s="17">
-        <f>SUM(E10:E163)</f>
+      <c r="C165" s="16"/>
+      <c r="D165" s="36"/>
+      <c r="E165" s="17">
+        <f>SUM(E10:E164)</f>
         <v>0</v>
       </c>
-      <c r="F164" s="17"/>
-      <c r="G164" s="17">
-        <f>SUM(G11:G163)</f>
+      <c r="F165" s="17"/>
+      <c r="G165" s="17">
+        <f>SUM(G11:G164)</f>
         <v>0</v>
       </c>
-      <c r="H164" s="17"/>
-      <c r="I164" s="17"/>
-      <c r="J164" s="17"/>
-    </row>
-    <row r="165" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="37"/>
-      <c r="C165" s="18"/>
-      <c r="D165" s="40"/>
-      <c r="F165" s="19"/>
-      <c r="G165" s="19"/>
-      <c r="H165" s="20"/>
-      <c r="I165" s="20"/>
-      <c r="J165" s="21"/>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H165" s="17"/>
+      <c r="I165" s="17"/>
+      <c r="J165" s="17"/>
+    </row>
+    <row r="166" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B166" s="37"/>
       <c r="C166" s="18"/>
       <c r="D166" s="40"/>
@@ -10513,21 +10530,21 @@
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
       <c r="C173" s="18"/>
-      <c r="D173" s="53"/>
-      <c r="E173" s="4"/>
-      <c r="F173" s="53"/>
-      <c r="G173" s="57"/>
-      <c r="H173" s="51"/>
+      <c r="D173" s="40"/>
+      <c r="F173" s="19"/>
+      <c r="G173" s="19"/>
+      <c r="H173" s="20"/>
       <c r="I173" s="20"/>
       <c r="J173" s="21"/>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B174" s="37"/>
       <c r="C174" s="18"/>
-      <c r="D174" s="40"/>
-      <c r="F174" s="19"/>
-      <c r="G174" s="19"/>
-      <c r="H174" s="20"/>
+      <c r="D174" s="53"/>
+      <c r="E174" s="4"/>
+      <c r="F174" s="53"/>
+      <c r="G174" s="57"/>
+      <c r="H174" s="51"/>
       <c r="I174" s="20"/>
       <c r="J174" s="21"/>
     </row>
@@ -25671,13 +25688,23 @@
       <c r="I1688" s="20"/>
       <c r="J1688" s="21"/>
     </row>
+    <row r="1689" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1689" s="37"/>
+      <c r="C1689" s="18"/>
+      <c r="D1689" s="40"/>
+      <c r="F1689" s="19"/>
+      <c r="G1689" s="19"/>
+      <c r="H1689" s="20"/>
+      <c r="I1689" s="20"/>
+      <c r="J1689" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J164" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J165" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D173">
+  <conditionalFormatting sqref="D174">
     <cfRule type="duplicateValues" dxfId="312" priority="1"/>
     <cfRule type="duplicateValues" dxfId="311" priority="2"/>
     <cfRule type="duplicateValues" dxfId="310" priority="3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время филиал на .xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время филиал на .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C2386E-81D3-4AF7-8FD4-4288D58776DE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EAEDAB2-EDAA-4AF1-B497-B169B04F00C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$165</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$601</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$601</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$164</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$600</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$600</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -489,7 +489,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="225">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -5520,7 +5520,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AX1689"/>
+  <dimension ref="A1:AX1688"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -8709,7 +8709,7 @@
     </row>
     <row r="106" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A106" s="55" t="str">
-        <f t="shared" ref="A106:A140" si="20">RIGHT(D106,4)</f>
+        <f t="shared" ref="A106:A139" si="20">RIGHT(D106,4)</f>
         <v>3582</v>
       </c>
       <c r="B106" s="53" t="s">
@@ -9410,7 +9410,7 @@
         <v>0.15</v>
       </c>
       <c r="G129" s="23">
-        <f t="shared" ref="G129:G139" si="26">E129*F129</f>
+        <f t="shared" ref="G129:G138" si="26">E129*F129</f>
         <v>0</v>
       </c>
       <c r="H129" s="14">
@@ -9634,27 +9634,27 @@
     <row r="137" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6557</v>
+        <v>5679</v>
       </c>
       <c r="B137" s="53" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C137" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D137" s="51">
-        <v>1001200756557</v>
+        <v>1001190765679</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G137" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H137" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I137" s="14">
         <v>60</v>
@@ -9664,163 +9664,163 @@
     <row r="138" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>5679</v>
+        <v>5677</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C138" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D138" s="51">
-        <v>1001190765679</v>
+        <v>1001190715677</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G138" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H138" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I138" s="14">
         <v>60</v>
       </c>
       <c r="J138" s="29"/>
     </row>
-    <row r="139" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>5677</v>
+        <v>7414</v>
       </c>
       <c r="B139" s="53" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D139" s="51">
-        <v>1001190715677</v>
+        <v>1001204447414</v>
       </c>
       <c r="E139" s="24"/>
       <c r="F139" s="23">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G139" s="23">
-        <f t="shared" si="26"/>
+        <f>E139</f>
         <v>0</v>
       </c>
       <c r="H139" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I139" s="14">
         <v>60</v>
       </c>
       <c r="J139" s="29"/>
     </row>
-    <row r="140" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="55" t="str">
-        <f t="shared" si="20"/>
-        <v>7414</v>
-      </c>
-      <c r="B140" s="53" t="s">
-        <v>159</v>
-      </c>
-      <c r="C140" s="50" t="s">
+    <row r="140" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="B140" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C140" s="42"/>
+      <c r="D140" s="42"/>
+      <c r="E140" s="24"/>
+      <c r="F140" s="41"/>
+      <c r="G140" s="42"/>
+      <c r="H140" s="42"/>
+      <c r="I140" s="42"/>
+      <c r="J140" s="43"/>
+    </row>
+    <row r="141" spans="1:10" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="55" t="str">
+        <f t="shared" ref="A141:A150" si="27">RIGHT(D141,4)</f>
+        <v>4584</v>
+      </c>
+      <c r="B141" s="98" t="s">
+        <v>125</v>
+      </c>
+      <c r="C141" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D140" s="51">
-        <v>1001204447414</v>
-      </c>
-      <c r="E140" s="24"/>
-      <c r="F140" s="23">
-        <v>1</v>
-      </c>
-      <c r="G140" s="23">
-        <f>E140</f>
+      <c r="D141" s="97">
+        <v>1001092674584</v>
+      </c>
+      <c r="E141" s="24"/>
+      <c r="F141" s="23">
+        <v>2.5</v>
+      </c>
+      <c r="G141" s="23">
+        <f>E141</f>
         <v>0</v>
       </c>
-      <c r="H140" s="14">
-        <v>8</v>
-      </c>
-      <c r="I140" s="14">
+      <c r="H141" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="I141" s="14">
         <v>60</v>
       </c>
-      <c r="J140" s="29"/>
-    </row>
-    <row r="141" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="B141" s="42" t="s">
-        <v>92</v>
-      </c>
-      <c r="C141" s="42"/>
-      <c r="D141" s="42"/>
-      <c r="E141" s="24"/>
-      <c r="F141" s="41"/>
-      <c r="G141" s="42"/>
-      <c r="H141" s="42"/>
-      <c r="I141" s="42"/>
-      <c r="J141" s="43"/>
-    </row>
-    <row r="142" spans="1:10" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J141" s="29"/>
+    </row>
+    <row r="142" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="55" t="str">
-        <f t="shared" ref="A142:A151" si="27">RIGHT(D142,4)</f>
-        <v>4584</v>
+        <f t="shared" si="27"/>
+        <v>6495</v>
       </c>
       <c r="B142" s="98" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D142" s="97">
-        <v>1001092674584</v>
+        <v>21</v>
+      </c>
+      <c r="D142" s="51">
+        <v>1001092436495</v>
       </c>
       <c r="E142" s="24"/>
-      <c r="F142" s="23">
-        <v>2.5</v>
+      <c r="F142" s="56">
+        <v>0.3</v>
       </c>
       <c r="G142" s="23">
-        <f>E142</f>
+        <f>E142*F142</f>
         <v>0</v>
       </c>
-      <c r="H142" s="14">
-        <v>7.5</v>
-      </c>
-      <c r="I142" s="14">
-        <v>60</v>
+      <c r="H142" s="29">
+        <v>1.8</v>
+      </c>
+      <c r="I142" s="29">
+        <v>45</v>
       </c>
       <c r="J142" s="29"/>
     </row>
     <row r="143" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>6495</v>
-      </c>
-      <c r="B143" s="98" t="s">
-        <v>97</v>
+        <v>6470</v>
+      </c>
+      <c r="B143" s="95" t="s">
+        <v>126</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D143" s="51">
-        <v>1001092436495</v>
+        <v>1001092436470</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="56">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="G143" s="23">
-        <f>E143*F143</f>
+        <f t="shared" ref="G143:G144" si="28">E143</f>
         <v>0</v>
       </c>
       <c r="H143" s="29">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="I143" s="29">
         <v>45</v>
@@ -9830,57 +9830,57 @@
     <row r="144" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>6470</v>
+        <v>5452</v>
       </c>
       <c r="B144" s="95" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="C144" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D144" s="51">
-        <v>1001092436470</v>
+        <v>1001092485452</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="56">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="G144" s="23">
-        <f t="shared" ref="G144:G145" si="28">E144</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H144" s="29">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="I144" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J144" s="29"/>
     </row>
     <row r="145" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>5452</v>
+        <v>3215</v>
       </c>
       <c r="B145" s="95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D145" s="51">
-        <v>1001092485452</v>
+        <v>1001094053215</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="56">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G145" s="23">
-        <f t="shared" si="28"/>
+        <f>E145*F145</f>
         <v>0</v>
       </c>
       <c r="H145" s="29">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I145" s="29">
         <v>60</v>
@@ -9890,57 +9890,57 @@
     <row r="146" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>3215</v>
+        <v>6866</v>
       </c>
       <c r="B146" s="95" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D146" s="51">
-        <v>1001094053215</v>
+        <v>1001095716866</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="56">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G146" s="23">
-        <f>E146*F146</f>
+        <f>E146</f>
         <v>0</v>
       </c>
       <c r="H146" s="29">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I146" s="29">
         <v>60</v>
       </c>
       <c r="J146" s="29"/>
     </row>
-    <row r="147" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>6866</v>
-      </c>
-      <c r="B147" s="95" t="s">
-        <v>93</v>
+        <v>5495</v>
+      </c>
+      <c r="B147" s="53" t="s">
+        <v>96</v>
       </c>
       <c r="C147" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D147" s="51">
-        <v>1001095716866</v>
+        <v>21</v>
+      </c>
+      <c r="D147" s="96">
+        <v>1001093345495</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="56">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G147" s="23">
-        <f>E147</f>
+        <f t="shared" ref="G147:G149" si="29">E147*F147</f>
         <v>0</v>
       </c>
       <c r="H147" s="29">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="I147" s="29">
         <v>60</v>
@@ -9950,159 +9950,159 @@
     <row r="148" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>5495</v>
+        <v>7377</v>
       </c>
       <c r="B148" s="53" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="C148" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D148" s="96">
-        <v>1001093345495</v>
+        <v>1001095027377</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="56">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G148" s="23">
-        <f t="shared" ref="G148:G150" si="29">E148*F148</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H148" s="29">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="I148" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J148" s="29"/>
     </row>
     <row r="149" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>7377</v>
+        <v>6925</v>
       </c>
       <c r="B149" s="53" t="s">
-        <v>127</v>
+        <v>214</v>
       </c>
       <c r="C149" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D149" s="96">
-        <v>1001095027377</v>
+        <v>1001095226925</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="56">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="G149" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H149" s="29">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="I149" s="29">
         <v>45</v>
       </c>
       <c r="J149" s="29"/>
     </row>
-    <row r="150" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>6925</v>
+        <v>6025</v>
       </c>
       <c r="B150" s="53" t="s">
-        <v>214</v>
+        <v>128</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D150" s="96">
-        <v>1001095226925</v>
+        <v>1001094966025</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="56">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="G150" s="23">
-        <f t="shared" si="29"/>
+        <f>E150</f>
         <v>0</v>
       </c>
       <c r="H150" s="29">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="I150" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J150" s="29"/>
     </row>
-    <row r="151" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="55" t="str">
-        <f t="shared" si="27"/>
-        <v>6025</v>
-      </c>
-      <c r="B151" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="C151" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D151" s="96">
-        <v>1001094966025</v>
-      </c>
+    <row r="151" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="B151" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C151" s="42"/>
+      <c r="D151" s="42"/>
       <c r="E151" s="24"/>
-      <c r="F151" s="56">
-        <v>3</v>
-      </c>
-      <c r="G151" s="23">
-        <f>E151</f>
+      <c r="F151" s="41"/>
+      <c r="G151" s="42"/>
+      <c r="H151" s="42"/>
+      <c r="I151" s="42"/>
+      <c r="J151" s="43"/>
+    </row>
+    <row r="152" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="55" t="str">
+        <f t="shared" ref="A152:A163" si="30">RIGHT(D152,4)</f>
+        <v>7090</v>
+      </c>
+      <c r="B152" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C152" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152" s="51">
+        <v>1001084217090</v>
+      </c>
+      <c r="E152" s="24"/>
+      <c r="F152" s="23">
+        <v>0.3</v>
+      </c>
+      <c r="G152" s="23">
+        <f t="shared" ref="G152:G153" si="31">E152*F152</f>
         <v>0</v>
       </c>
-      <c r="H151" s="29">
-        <v>6</v>
-      </c>
-      <c r="I151" s="29">
-        <v>60</v>
-      </c>
-      <c r="J151" s="29"/>
-    </row>
-    <row r="152" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="47" t="s">
-        <v>109</v>
-      </c>
-      <c r="B152" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="C152" s="42"/>
-      <c r="D152" s="42"/>
-      <c r="E152" s="24"/>
-      <c r="F152" s="41"/>
-      <c r="G152" s="42"/>
-      <c r="H152" s="42"/>
-      <c r="I152" s="42"/>
-      <c r="J152" s="43"/>
-    </row>
-    <row r="153" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H152" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="I152" s="14">
+        <v>50</v>
+      </c>
+      <c r="J152" s="29"/>
+    </row>
+    <row r="153" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="55" t="str">
-        <f t="shared" ref="A153:A164" si="30">RIGHT(D153,4)</f>
-        <v>7090</v>
+        <f t="shared" si="30"/>
+        <v>7187</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C153" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D153" s="51">
-        <v>1001084217090</v>
+        <v>1001085637187</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="23">
         <v>0.3</v>
       </c>
       <c r="G153" s="23">
-        <f t="shared" ref="G153:G154" si="31">E153*F153</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H153" s="14">
@@ -10116,111 +10116,111 @@
     <row r="154" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>7187</v>
+        <v>6620</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D154" s="51">
-        <v>1001085637187</v>
+        <v>1001081596620</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
-        <v>0.3</v>
+        <v>1.05</v>
       </c>
       <c r="G154" s="23">
-        <f t="shared" si="31"/>
+        <f>E154</f>
         <v>0</v>
       </c>
       <c r="H154" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I154" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J154" s="29"/>
     </row>
     <row r="155" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6620</v>
+        <v>6008</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>99</v>
+        <v>223</v>
       </c>
       <c r="C155" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D155" s="51">
-        <v>1001081596620</v>
+        <v>1001084856008</v>
       </c>
       <c r="E155" s="24"/>
-      <c r="F155" s="23">
-        <v>1.05</v>
-      </c>
+      <c r="F155" s="23"/>
       <c r="G155" s="23">
         <f>E155</f>
         <v>0</v>
       </c>
-      <c r="H155" s="14">
-        <v>3.15</v>
-      </c>
-      <c r="I155" s="14">
-        <v>30</v>
-      </c>
+      <c r="H155" s="14"/>
+      <c r="I155" s="14"/>
       <c r="J155" s="29"/>
     </row>
     <row r="156" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6008</v>
+        <v>7103</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D156" s="51">
-        <v>1001084856008</v>
+        <v>1001223297103</v>
       </c>
       <c r="E156" s="24"/>
-      <c r="F156" s="23"/>
+      <c r="F156" s="23">
+        <v>0.18</v>
+      </c>
       <c r="G156" s="23">
-        <f>E156</f>
+        <f t="shared" ref="G156:G163" si="32">E156*F156</f>
         <v>0</v>
       </c>
-      <c r="H156" s="14"/>
-      <c r="I156" s="14"/>
+      <c r="H156" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="I156" s="14">
+        <v>50</v>
+      </c>
       <c r="J156" s="29"/>
     </row>
     <row r="157" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="55" t="str">
-        <f t="shared" si="30"/>
-        <v>7103</v>
+        <f>RIGHT(D157,4)</f>
+        <v>7092</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="C157" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D157" s="51">
-        <v>1001223297103</v>
+        <v>1001223297092</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G157" s="23">
-        <f t="shared" ref="G157:G164" si="32">E157*F157</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="I157" s="14">
         <v>50</v>
@@ -10229,58 +10229,58 @@
     </row>
     <row r="158" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="55" t="str">
-        <f>RIGHT(D158,4)</f>
-        <v>7092</v>
+        <f t="shared" si="30"/>
+        <v>6228</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D158" s="51">
-        <v>1001223297092</v>
+        <v>1001225416228</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="G158" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H158" s="14">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="I158" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J158" s="29"/>
     </row>
     <row r="159" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6228</v>
+        <v>6448</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D159" s="51">
-        <v>1001225416228</v>
+        <v>1001234146448</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G159" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H159" s="14">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I159" s="14">
         <v>45</v>
@@ -10290,27 +10290,27 @@
     <row r="160" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6448</v>
+        <v>6208</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="C160" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D160" s="51">
-        <v>1001234146448</v>
+        <v>1001220226208</v>
       </c>
       <c r="E160" s="24"/>
       <c r="F160" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G160" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H160" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I160" s="14">
         <v>45</v>
@@ -10320,144 +10320,124 @@
     <row r="161" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6208</v>
+        <v>6754</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="C161" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D161" s="51">
-        <v>1001220226208</v>
+        <v>1001225406754</v>
       </c>
       <c r="E161" s="24"/>
       <c r="F161" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G161" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H161" s="14">
-        <v>1.5</v>
+        <v>0.72</v>
       </c>
       <c r="I161" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J161" s="29"/>
     </row>
     <row r="162" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6754</v>
+        <v>6279</v>
       </c>
       <c r="B162" s="35" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="C162" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D162" s="51">
-        <v>1001225406754</v>
+        <v>1001220286279</v>
       </c>
       <c r="E162" s="24"/>
       <c r="F162" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G162" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H162" s="14">
-        <v>0.72</v>
+        <v>1.2</v>
       </c>
       <c r="I162" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J162" s="29"/>
     </row>
-    <row r="163" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6279</v>
+        <v>7288</v>
       </c>
       <c r="B163" s="35" t="s">
-        <v>100</v>
+        <v>213</v>
       </c>
       <c r="C163" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D163" s="51">
-        <v>1001220286279</v>
+        <v>1001223907288</v>
       </c>
       <c r="E163" s="24"/>
       <c r="F163" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G163" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H163" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I163" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J163" s="29"/>
     </row>
-    <row r="164" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="55" t="str">
-        <f t="shared" si="30"/>
-        <v>7288</v>
-      </c>
-      <c r="B164" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="C164" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D164" s="51">
-        <v>1001223907288</v>
-      </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="23">
-        <v>0.1</v>
-      </c>
-      <c r="G164" s="23">
-        <f t="shared" si="32"/>
+    <row r="164" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="48"/>
+      <c r="B164" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="C164" s="16"/>
+      <c r="D164" s="36"/>
+      <c r="E164" s="17">
+        <f>SUM(E10:E163)</f>
         <v>0</v>
       </c>
-      <c r="H164" s="14">
-        <v>1</v>
-      </c>
-      <c r="I164" s="14">
-        <v>60</v>
-      </c>
-      <c r="J164" s="29"/>
-    </row>
-    <row r="165" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="48"/>
-      <c r="B165" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="C165" s="16"/>
-      <c r="D165" s="36"/>
-      <c r="E165" s="17">
-        <f>SUM(E10:E164)</f>
+      <c r="F164" s="17"/>
+      <c r="G164" s="17">
+        <f>SUM(G11:G163)</f>
         <v>0</v>
       </c>
-      <c r="F165" s="17"/>
-      <c r="G165" s="17">
-        <f>SUM(G11:G164)</f>
-        <v>0</v>
-      </c>
-      <c r="H165" s="17"/>
-      <c r="I165" s="17"/>
-      <c r="J165" s="17"/>
-    </row>
-    <row r="166" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H164" s="17"/>
+      <c r="I164" s="17"/>
+      <c r="J164" s="17"/>
+    </row>
+    <row r="165" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B165" s="37"/>
+      <c r="C165" s="18"/>
+      <c r="D165" s="40"/>
+      <c r="F165" s="19"/>
+      <c r="G165" s="19"/>
+      <c r="H165" s="20"/>
+      <c r="I165" s="20"/>
+      <c r="J165" s="21"/>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B166" s="37"/>
       <c r="C166" s="18"/>
       <c r="D166" s="40"/>
@@ -10530,21 +10510,21 @@
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
       <c r="C173" s="18"/>
-      <c r="D173" s="40"/>
-      <c r="F173" s="19"/>
-      <c r="G173" s="19"/>
-      <c r="H173" s="20"/>
+      <c r="D173" s="53"/>
+      <c r="E173" s="4"/>
+      <c r="F173" s="53"/>
+      <c r="G173" s="57"/>
+      <c r="H173" s="51"/>
       <c r="I173" s="20"/>
       <c r="J173" s="21"/>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B174" s="37"/>
       <c r="C174" s="18"/>
-      <c r="D174" s="53"/>
-      <c r="E174" s="4"/>
-      <c r="F174" s="53"/>
-      <c r="G174" s="57"/>
-      <c r="H174" s="51"/>
+      <c r="D174" s="40"/>
+      <c r="F174" s="19"/>
+      <c r="G174" s="19"/>
+      <c r="H174" s="20"/>
       <c r="I174" s="20"/>
       <c r="J174" s="21"/>
     </row>
@@ -25688,23 +25668,13 @@
       <c r="I1688" s="20"/>
       <c r="J1688" s="21"/>
     </row>
-    <row r="1689" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B1689" s="37"/>
-      <c r="C1689" s="18"/>
-      <c r="D1689" s="40"/>
-      <c r="F1689" s="19"/>
-      <c r="G1689" s="19"/>
-      <c r="H1689" s="20"/>
-      <c r="I1689" s="20"/>
-      <c r="J1689" s="21"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A9:J165" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J164" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D174">
+  <conditionalFormatting sqref="D173">
     <cfRule type="duplicateValues" dxfId="312" priority="1"/>
     <cfRule type="duplicateValues" dxfId="311" priority="2"/>
     <cfRule type="duplicateValues" dxfId="310" priority="3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время филиал на .xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время филиал на .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EAEDAB2-EDAA-4AF1-B497-B169B04F00C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDDD2FC-0B66-4D65-A738-DB57FED25D67}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$164</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$600</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$600</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$165</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$601</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$601</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -489,7 +489,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="225">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1100,9 +1100,6 @@
     <t xml:space="preserve">130438120 ООО "НОВОЕ ВРЕМЯ"  93 Донецк г      Чаадаева ул.д.1        </t>
   </si>
   <si>
-    <t>Бердянск</t>
-  </si>
-  <si>
     <t>САЛЯМИ ИТАЛЬЯНСКАЯ с/к в/у 1/250*8_120c</t>
   </si>
   <si>
@@ -1164,6 +1161,9 @@
   </si>
   <si>
     <t>НАБОР ДЛЯ ПИЦЦЫ с/к с/н мгс 3*3_HRC</t>
+  </si>
+  <si>
+    <t>СЕРВЕЛАТ КРЕМЛЕВСКИЙ в/к в/у 0.84кг</t>
   </si>
 </sst>
 </file>
@@ -5520,7 +5520,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AX1688"/>
+  <dimension ref="A1:AX1689"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -5574,17 +5574,18 @@
         <v>2</v>
       </c>
       <c r="D3" s="54">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="54">
         <f>D3+3</f>
-        <v>46212</v>
-      </c>
-      <c r="G3" s="105" t="s">
-        <v>203</v>
+        <v>46219</v>
+      </c>
+      <c r="G3" s="105" t="str">
+        <f>VLOOKUP(D1,K:L,2,0)</f>
+        <v>130438122 ООО "НОВОЕ ВРЕМЯ"  272151 Бердянский р-н 90  Трояны</v>
       </c>
       <c r="H3" s="103"/>
       <c r="I3" s="103"/>
@@ -5601,7 +5602,7 @@
         <v>130439104</v>
       </c>
       <c r="L4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:50" x14ac:dyDescent="0.25">
@@ -6333,7 +6334,7 @@
         <v>6392</v>
       </c>
       <c r="B25" s="53" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C25" s="50" t="s">
         <v>21</v>
@@ -6363,7 +6364,7 @@
         <v>5851</v>
       </c>
       <c r="B26" s="53" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C26" s="50" t="s">
         <v>23</v>
@@ -6393,7 +6394,7 @@
         <v>7632</v>
       </c>
       <c r="B27" s="53" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C27" s="50" t="s">
         <v>21</v>
@@ -6713,7 +6714,7 @@
         <v>6602</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C38" s="50" t="s">
         <v>21</v>
@@ -6743,7 +6744,7 @@
         <v>7284</v>
       </c>
       <c r="B39" s="53" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C39" s="50" t="s">
         <v>21</v>
@@ -6803,7 +6804,7 @@
         <v>7461</v>
       </c>
       <c r="B41" s="53" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C41" s="50" t="s">
         <v>21</v>
@@ -6925,7 +6926,7 @@
         <v>6829</v>
       </c>
       <c r="B45" s="53" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C45" s="50" t="s">
         <v>23</v>
@@ -7135,7 +7136,7 @@
         <v>6303</v>
       </c>
       <c r="B52" s="53" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C52" s="50" t="s">
         <v>23</v>
@@ -7555,7 +7556,7 @@
         <v>6661</v>
       </c>
       <c r="B66" s="53" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C66" s="50" t="s">
         <v>23</v>
@@ -7751,7 +7752,7 @@
         <v>6550</v>
       </c>
       <c r="B73" s="91" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C73" s="100" t="s">
         <v>23</v>
@@ -7841,7 +7842,7 @@
         <v>6527</v>
       </c>
       <c r="B76" s="91" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C76" s="50" t="s">
         <v>23</v>
@@ -7973,7 +7974,7 @@
     </row>
     <row r="81" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A81" s="55" t="str">
-        <f t="shared" ref="A81:A104" si="16">RIGHT(D81,4)</f>
+        <f t="shared" ref="A81:A105" si="16">RIGHT(D81,4)</f>
         <v>7564</v>
       </c>
       <c r="B81" s="53" t="s">
@@ -8022,7 +8023,7 @@
         <v>0.33</v>
       </c>
       <c r="G82" s="23">
-        <f t="shared" ref="G82:G93" si="17">E82*F82</f>
+        <f t="shared" ref="G82:G94" si="17">E82*F82</f>
         <v>0</v>
       </c>
       <c r="H82" s="14">
@@ -8188,87 +8189,83 @@
     <row r="88" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>6807</v>
+        <v>6946</v>
       </c>
       <c r="B88" s="53" t="s">
-        <v>76</v>
+        <v>224</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D88" s="51">
-        <v>1001300366807</v>
+        <v>1001300456946</v>
       </c>
       <c r="E88" s="24"/>
       <c r="F88" s="56">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="G88" s="23">
-        <f t="shared" si="17"/>
+        <f>E88</f>
         <v>0</v>
       </c>
-      <c r="H88" s="29">
-        <v>2.64</v>
-      </c>
-      <c r="I88" s="29">
-        <v>45</v>
-      </c>
+      <c r="H88" s="29"/>
+      <c r="I88" s="29"/>
       <c r="J88" s="29"/>
     </row>
     <row r="89" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7154</v>
+        <v>6807</v>
       </c>
       <c r="B89" s="53" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C89" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D89" s="51">
-        <v>1001300387154</v>
+        <v>1001300366807</v>
       </c>
       <c r="E89" s="24"/>
-      <c r="F89" s="23">
-        <v>0.35</v>
+      <c r="F89" s="56">
+        <v>0.33</v>
       </c>
       <c r="G89" s="23">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H89" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I89" s="14">
-        <v>50</v>
+      <c r="H89" s="29">
+        <v>2.64</v>
+      </c>
+      <c r="I89" s="29">
+        <v>45</v>
       </c>
       <c r="J89" s="29"/>
     </row>
     <row r="90" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7157</v>
+        <v>7154</v>
       </c>
       <c r="B90" s="53" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C90" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D90" s="51">
-        <v>1001300387157</v>
+        <v>1001300387154</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="23">
-        <v>0.63</v>
+        <v>0.35</v>
       </c>
       <c r="G90" s="23">
-        <f>E90</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H90" s="14">
-        <v>5.04</v>
+        <v>2.8</v>
       </c>
       <c r="I90" s="14">
         <v>50</v>
@@ -8278,143 +8275,143 @@
     <row r="91" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7236</v>
+        <v>7157</v>
       </c>
       <c r="B91" s="53" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D91" s="51">
-        <v>1001304507236</v>
+        <v>1001300387157</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.63</v>
       </c>
       <c r="G91" s="23">
-        <f t="shared" si="17"/>
+        <f>E91</f>
         <v>0</v>
       </c>
       <c r="H91" s="14">
-        <v>2.2400000000000002</v>
+        <v>5.04</v>
       </c>
       <c r="I91" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J91" s="29"/>
     </row>
     <row r="92" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7489</v>
+        <v>7236</v>
       </c>
       <c r="B92" s="53" t="s">
-        <v>221</v>
+        <v>69</v>
       </c>
       <c r="C92" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D92" s="51">
-        <v>1001307357489</v>
+        <v>1001304507236</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="23">
         <v>0.28000000000000003</v>
       </c>
       <c r="G92" s="23">
-        <f t="shared" ref="G92" si="18">E92*F92</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H92" s="14"/>
-      <c r="I92" s="14"/>
+      <c r="H92" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I92" s="14">
+        <v>45</v>
+      </c>
       <c r="J92" s="29"/>
     </row>
     <row r="93" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>6787</v>
-      </c>
-      <c r="B93" s="99" t="s">
-        <v>66</v>
+        <v>7489</v>
+      </c>
+      <c r="B93" s="53" t="s">
+        <v>220</v>
       </c>
       <c r="C93" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D93" s="51">
-        <v>1001300456787</v>
+        <v>1001307357489</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
-        <v>0.33</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G93" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="G93" si="18">E93*F93</f>
         <v>0</v>
       </c>
-      <c r="H93" s="14">
-        <v>2.64</v>
-      </c>
-      <c r="I93" s="14">
-        <v>45</v>
-      </c>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
       <c r="J93" s="29"/>
     </row>
     <row r="94" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7166</v>
+        <v>6787</v>
       </c>
       <c r="B94" s="99" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D94" s="51">
-        <v>1001303987166</v>
+        <v>1001300456787</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="G94" s="23">
-        <f>E94</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H94" s="14">
-        <v>5.6</v>
+        <v>2.64</v>
       </c>
       <c r="I94" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J94" s="29"/>
     </row>
-    <row r="95" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7169</v>
-      </c>
-      <c r="B95" s="53" t="s">
-        <v>71</v>
+        <v>7166</v>
+      </c>
+      <c r="B95" s="99" t="s">
+        <v>72</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D95" s="51">
-        <v>1001303987169</v>
+        <v>1001303987166</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="23">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="G95" s="23">
-        <f>E95*F95</f>
+        <f>E95</f>
         <v>0</v>
       </c>
       <c r="H95" s="14">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="I95" s="14">
         <v>50</v>
@@ -8424,57 +8421,57 @@
     <row r="96" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>5544</v>
+        <v>7169</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D96" s="51">
-        <v>1001051875544</v>
+        <v>1001303987169</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.81</v>
+        <v>0.35</v>
       </c>
       <c r="G96" s="23">
-        <f>E96</f>
+        <f>E96*F96</f>
         <v>0</v>
       </c>
       <c r="H96" s="14">
-        <v>4.8600000000000003</v>
+        <v>2.8</v>
       </c>
       <c r="I96" s="14">
-        <v>45</v>
-      </c>
-      <c r="J96" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="J96" s="29"/>
     </row>
     <row r="97" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>6697</v>
+        <v>5544</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D97" s="51">
-        <v>1001301876697</v>
+        <v>1001051875544</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.35</v>
+        <v>0.81</v>
       </c>
       <c r="G97" s="23">
-        <f t="shared" ref="G97:G104" si="19">E97*F97</f>
+        <f>E97</f>
         <v>0</v>
       </c>
       <c r="H97" s="14">
-        <v>2.8</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I97" s="14">
         <v>45</v>
@@ -8484,27 +8481,27 @@
     <row r="98" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7237</v>
+        <v>6697</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C98" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D98" s="51">
-        <v>1001304497237</v>
+        <v>1001301876697</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G98" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="G98:G105" si="19">E98*F98</f>
         <v>0</v>
       </c>
       <c r="H98" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I98" s="14">
         <v>45</v>
@@ -8514,27 +8511,27 @@
     <row r="99" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7238</v>
+        <v>7237</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="C99" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D99" s="51">
-        <v>1001305197238</v>
+        <v>1001304497237</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="23">
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G99" s="23">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H99" s="14">
-        <v>2.48</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I99" s="14">
         <v>45</v>
@@ -8544,57 +8541,57 @@
     <row r="100" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7177</v>
+        <v>7238</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C100" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D100" s="51">
-        <v>1001302347177</v>
+        <v>1001305197238</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="23">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="G100" s="23">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H100" s="14">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="I100" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J100" s="49"/>
     </row>
     <row r="101" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7332</v>
+        <v>7177</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="C101" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D101" s="51">
-        <v>1001301777332</v>
+        <v>1001302347177</v>
       </c>
       <c r="E101" s="24"/>
       <c r="F101" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G101" s="23">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H101" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I101" s="14">
         <v>50</v>
@@ -8604,16 +8601,16 @@
     <row r="102" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7333</v>
+        <v>7332</v>
       </c>
       <c r="B102" s="53" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C102" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D102" s="51">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="E102" s="24"/>
       <c r="F102" s="23">
@@ -8634,46 +8631,46 @@
     <row r="103" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>6459</v>
+        <v>7333</v>
       </c>
       <c r="B103" s="53" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C103" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D103" s="51">
-        <v>1001214196459</v>
+        <v>1001303987333</v>
       </c>
       <c r="E103" s="24"/>
       <c r="F103" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G103" s="23">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H103" s="14">
-        <v>1</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I103" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J103" s="49"/>
     </row>
-    <row r="104" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="55" t="str">
         <f t="shared" si="16"/>
-        <v>7474</v>
+        <v>6459</v>
       </c>
       <c r="B104" s="53" t="s">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="C104" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D104" s="51">
-        <v>1001216717474</v>
+        <v>1001214196459</v>
       </c>
       <c r="E104" s="24"/>
       <c r="F104" s="23">
@@ -8691,76 +8688,76 @@
       </c>
       <c r="J104" s="49"/>
     </row>
-    <row r="105" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="47" t="s">
+    <row r="105" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="55" t="str">
+        <f t="shared" si="16"/>
+        <v>7474</v>
+      </c>
+      <c r="B105" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C105" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105" s="51">
+        <v>1001216717474</v>
+      </c>
+      <c r="E105" s="24"/>
+      <c r="F105" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G105" s="23">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H105" s="14">
+        <v>1</v>
+      </c>
+      <c r="I105" s="14">
+        <v>45</v>
+      </c>
+      <c r="J105" s="49"/>
+    </row>
+    <row r="106" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B105" s="42" t="s">
+      <c r="B106" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C105" s="42"/>
-      <c r="D105" s="42"/>
-      <c r="E105" s="24"/>
-      <c r="F105" s="41"/>
-      <c r="G105" s="42"/>
-      <c r="H105" s="42"/>
-      <c r="I105" s="42"/>
-      <c r="J105" s="43"/>
-    </row>
-    <row r="106" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="55" t="str">
-        <f t="shared" ref="A106:A139" si="20">RIGHT(D106,4)</f>
+      <c r="C106" s="42"/>
+      <c r="D106" s="42"/>
+      <c r="E106" s="24"/>
+      <c r="F106" s="41"/>
+      <c r="G106" s="42"/>
+      <c r="H106" s="42"/>
+      <c r="I106" s="42"/>
+      <c r="J106" s="43"/>
+    </row>
+    <row r="107" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="55" t="str">
+        <f t="shared" ref="A107:A140" si="20">RIGHT(D107,4)</f>
         <v>3582</v>
       </c>
-      <c r="B106" s="53" t="s">
+      <c r="B107" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="C106" s="50" t="s">
+      <c r="C107" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D106" s="51">
+      <c r="D107" s="51">
         <v>1001061973582</v>
-      </c>
-      <c r="E106" s="24"/>
-      <c r="F106" s="56">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="G106" s="23">
-        <f>E106</f>
-        <v>0</v>
-      </c>
-      <c r="H106" s="94">
-        <v>3.9</v>
-      </c>
-      <c r="I106" s="93">
-        <v>120</v>
-      </c>
-      <c r="J106" s="29"/>
-    </row>
-    <row r="107" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="55" t="str">
-        <f t="shared" si="20"/>
-        <v>3986</v>
-      </c>
-      <c r="B107" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="C107" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D107" s="51">
-        <v>1001061973986</v>
       </c>
       <c r="E107" s="24"/>
       <c r="F107" s="56">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G107" s="23">
-        <f t="shared" ref="G107:G112" si="21">E107*F107</f>
+        <f>E107</f>
         <v>0</v>
       </c>
       <c r="H107" s="94">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I107" s="93">
         <v>120</v>
@@ -8770,29 +8767,29 @@
     <row r="108" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>5931</v>
+        <v>3986</v>
       </c>
       <c r="B108" s="53" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C108" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D108" s="51">
-        <v>1001060755931</v>
+        <v>1001061973986</v>
       </c>
       <c r="E108" s="24"/>
-      <c r="F108" s="23">
-        <v>0.22</v>
+      <c r="F108" s="56">
+        <v>0.25</v>
       </c>
       <c r="G108" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G108:G113" si="21">E108*F108</f>
         <v>0</v>
       </c>
-      <c r="H108" s="92">
-        <v>1.76</v>
-      </c>
-      <c r="I108" s="14">
+      <c r="H108" s="94">
+        <v>2</v>
+      </c>
+      <c r="I108" s="93">
         <v>120</v>
       </c>
       <c r="J108" s="29"/>
@@ -8800,27 +8797,27 @@
     <row r="109" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>5708</v>
+        <v>5931</v>
       </c>
       <c r="B109" s="53" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C109" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D109" s="51">
-        <v>1001063145708</v>
+        <v>1001060755931</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="23">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="G109" s="23">
-        <f t="shared" ref="G109:G110" si="22">E109</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H109" s="14">
-        <v>4</v>
+      <c r="H109" s="92">
+        <v>1.76</v>
       </c>
       <c r="I109" s="14">
         <v>120</v>
@@ -8830,27 +8827,27 @@
     <row r="110" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>3287</v>
+        <v>5708</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C110" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D110" s="51">
-        <v>1001060763287</v>
+        <v>1001063145708</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.48799999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G110" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G110:G111" si="22">E110</f>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I110" s="14">
         <v>120</v>
@@ -8860,27 +8857,27 @@
     <row r="111" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>4993</v>
+        <v>3287</v>
       </c>
       <c r="B111" s="53" t="s">
-        <v>204</v>
+        <v>91</v>
       </c>
       <c r="C111" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D111" s="51">
-        <v>1001060764993</v>
+        <v>1001060763287</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G111" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H111" s="14">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I111" s="14">
         <v>120</v>
@@ -8890,16 +8887,16 @@
     <row r="112" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>5483</v>
+        <v>4993</v>
       </c>
       <c r="B112" s="53" t="s">
-        <v>89</v>
+        <v>203</v>
       </c>
       <c r="C112" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D112" s="51">
-        <v>1001062505483</v>
+        <v>1001060764993</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
@@ -8920,27 +8917,27 @@
     <row r="113" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>4117</v>
+        <v>5483</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C113" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D113" s="51">
-        <v>1001062504117</v>
+        <v>1001062505483</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G113" s="23">
-        <f t="shared" ref="G113:G114" si="23">E113</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="I113" s="14">
         <v>120</v>
@@ -8950,27 +8947,27 @@
     <row r="114" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>0614</v>
+        <v>4117</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="C114" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D114" s="51">
-        <v>1001060720614</v>
+        <v>1001062504117</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.52</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G114" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G114:G115" si="23">E114</f>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>3.64</v>
+        <v>3.95</v>
       </c>
       <c r="I114" s="14">
         <v>120</v>
@@ -8980,27 +8977,27 @@
     <row r="115" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6967</v>
+        <v>0614</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="C115" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D115" s="51">
-        <v>1001063656967</v>
+        <v>1001060720614</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="G115" s="23">
-        <f t="shared" ref="G115:G125" si="24">E115*F115</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="I115" s="14">
         <v>120</v>
@@ -9010,23 +9007,23 @@
     <row r="116" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6937</v>
+        <v>6967</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="C116" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D116" s="51">
-        <v>1001063106937</v>
+        <v>1001063656967</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
         <v>0.25</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="G116:G126" si="24">E116*F116</f>
         <v>0</v>
       </c>
       <c r="H116" s="14">
@@ -9040,27 +9037,27 @@
     <row r="117" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7143</v>
+        <v>6937</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C117" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D117" s="51">
-        <v>1001060717143</v>
+        <v>1001063106937</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G117" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H117" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I117" s="14">
         <v>120</v>
@@ -9070,16 +9067,16 @@
     <row r="118" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7147</v>
+        <v>7143</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="C118" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D118" s="51">
-        <v>1001063237147</v>
+        <v>1001060717143</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
@@ -9100,57 +9097,57 @@
     <row r="119" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7456</v>
+        <v>7147</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>166</v>
+        <v>86</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D119" s="51">
-        <v>1001063097456</v>
+        <v>1001063237147</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G119" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I119" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J119" s="29"/>
     </row>
     <row r="120" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7364</v>
+        <v>7456</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C120" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="51">
-        <v>1001063217364</v>
+        <v>1001063097456</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G120" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I120" s="14">
         <v>90</v>
@@ -9160,16 +9157,16 @@
     <row r="121" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7383</v>
+        <v>7364</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C121" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D121" s="51">
-        <v>1001065467383</v>
+        <v>1001063217364</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
@@ -9190,57 +9187,57 @@
     <row r="122" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7317</v>
+        <v>7383</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C122" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D122" s="51">
-        <v>1001066567317</v>
+        <v>1001065467383</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G122" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I122" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J122" s="29"/>
     </row>
     <row r="123" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7318</v>
+        <v>7317</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C123" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D123" s="51">
-        <v>1001060727318</v>
+        <v>1001066567317</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G123" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <v>2.16</v>
+        <v>3.78</v>
       </c>
       <c r="I123" s="14">
         <v>120</v>
@@ -9250,27 +9247,27 @@
     <row r="124" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7316</v>
+        <v>7318</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C124" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D124" s="51">
-        <v>1001060727316</v>
+        <v>1001060727318</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G124" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="I124" s="14">
         <v>120</v>
@@ -9280,83 +9277,83 @@
     <row r="125" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7417</v>
+        <v>7316</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C125" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D125" s="51">
-        <v>1001307147417</v>
+        <v>1001060727316</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="G125" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>1.76</v>
+        <v>3.78</v>
       </c>
       <c r="I125" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J125" s="29"/>
     </row>
     <row r="126" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6832</v>
+        <v>7417</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D126" s="51">
-        <v>1001065616832</v>
+        <v>1001307147417</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
-        <v>0.215</v>
+        <v>0.44</v>
       </c>
       <c r="G126" s="23">
-        <f t="shared" ref="G126:G128" si="25">E126</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H126" s="14">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="I126" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="J126" s="29"/>
     </row>
     <row r="127" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7299</v>
+        <v>6832</v>
       </c>
       <c r="B127" s="53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C127" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D127" s="51">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="23">
         <v>0.215</v>
       </c>
       <c r="G127" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G127:G129" si="25">E127</f>
         <v>0</v>
       </c>
       <c r="H127" s="14">
@@ -9370,100 +9367,100 @@
     <row r="128" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7442</v>
+        <v>7299</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>224</v>
+        <v>83</v>
       </c>
       <c r="C128" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D128" s="51">
-        <v>1001200677442</v>
+        <v>1001060677299</v>
       </c>
       <c r="E128" s="24"/>
-      <c r="F128" s="23"/>
+      <c r="F128" s="23">
+        <v>0.215</v>
+      </c>
       <c r="G128" s="23">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="H128" s="14"/>
-      <c r="I128" s="14"/>
+      <c r="H128" s="14">
+        <v>2.15</v>
+      </c>
+      <c r="I128" s="14">
+        <v>30</v>
+      </c>
       <c r="J128" s="29"/>
     </row>
     <row r="129" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7386</v>
+        <v>7442</v>
       </c>
       <c r="B129" s="53" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
       <c r="C129" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D129" s="51">
-        <v>1001067017386</v>
+        <v>1001200677442</v>
       </c>
       <c r="E129" s="24"/>
-      <c r="F129" s="23">
-        <v>0.15</v>
-      </c>
+      <c r="F129" s="23"/>
       <c r="G129" s="23">
-        <f t="shared" ref="G129:G138" si="26">E129*F129</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="H129" s="14">
-        <v>1.35</v>
-      </c>
-      <c r="I129" s="14">
-        <v>90</v>
-      </c>
+      <c r="H129" s="14"/>
+      <c r="I129" s="14"/>
       <c r="J129" s="29"/>
     </row>
     <row r="130" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6454</v>
+        <v>7386</v>
       </c>
       <c r="B130" s="53" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="C130" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D130" s="51">
-        <v>1001201976454</v>
+        <v>1001067017386</v>
       </c>
       <c r="E130" s="24"/>
       <c r="F130" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G130" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="G130:G139" si="26">E130*F130</f>
         <v>0</v>
       </c>
       <c r="H130" s="14">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="I130" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J130" s="29"/>
     </row>
     <row r="131" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6834</v>
+        <v>6454</v>
       </c>
       <c r="B131" s="53" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C131" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D131" s="51">
-        <v>1001203146834</v>
+        <v>1001201976454</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="23">
@@ -9484,27 +9481,27 @@
     <row r="132" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7382</v>
+        <v>6834</v>
       </c>
       <c r="B132" s="53" t="s">
-        <v>85</v>
+        <v>217</v>
       </c>
       <c r="C132" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D132" s="51">
-        <v>1001203117382</v>
+        <v>1001203146834</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="23">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G132" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H132" s="14">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I132" s="14">
         <v>60</v>
@@ -9514,27 +9511,27 @@
     <row r="133" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6453</v>
+        <v>7382</v>
       </c>
       <c r="B133" s="53" t="s">
-        <v>208</v>
+        <v>85</v>
       </c>
       <c r="C133" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D133" s="51">
-        <v>1001202506453</v>
+        <v>1001203117382</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G133" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H133" s="14">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="I133" s="14">
         <v>60</v>
@@ -9544,27 +9541,27 @@
     <row r="134" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6221</v>
+        <v>6453</v>
       </c>
       <c r="B134" s="53" t="s">
-        <v>87</v>
+        <v>207</v>
       </c>
       <c r="C134" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D134" s="51">
-        <v>1001205376221</v>
+        <v>1001202506453</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G134" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H134" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I134" s="14">
         <v>60</v>
@@ -9574,16 +9571,16 @@
     <row r="135" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6222</v>
+        <v>6221</v>
       </c>
       <c r="B135" s="53" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="C135" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D135" s="51">
-        <v>1001205386222</v>
+        <v>1001205376221</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="23">
@@ -9604,27 +9601,27 @@
     <row r="136" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>6965</v>
+        <v>6222</v>
       </c>
       <c r="B136" s="53" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C136" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D136" s="51">
-        <v>1001206356965</v>
+        <v>1001205386222</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="23">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="G136" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H136" s="14">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="I136" s="14">
         <v>60</v>
@@ -9634,27 +9631,27 @@
     <row r="137" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>5679</v>
+        <v>6965</v>
       </c>
       <c r="B137" s="53" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C137" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D137" s="51">
-        <v>1001190765679</v>
+        <v>1001206356965</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="23">
-        <v>0.15</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G137" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H137" s="14">
-        <v>1.2</v>
+        <v>0.98</v>
       </c>
       <c r="I137" s="14">
         <v>60</v>
@@ -9664,163 +9661,163 @@
     <row r="138" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>5677</v>
+        <v>5679</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C138" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D138" s="51">
-        <v>1001190715677</v>
+        <v>1001190765679</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G138" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H138" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I138" s="14">
         <v>60</v>
       </c>
       <c r="J138" s="29"/>
     </row>
-    <row r="139" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="55" t="str">
         <f t="shared" si="20"/>
-        <v>7414</v>
+        <v>5677</v>
       </c>
       <c r="B139" s="53" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D139" s="51">
-        <v>1001204447414</v>
+        <v>1001190715677</v>
       </c>
       <c r="E139" s="24"/>
       <c r="F139" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G139" s="23">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H139" s="14">
         <v>1</v>
-      </c>
-      <c r="G139" s="23">
-        <f>E139</f>
-        <v>0</v>
-      </c>
-      <c r="H139" s="14">
-        <v>8</v>
       </c>
       <c r="I139" s="14">
         <v>60</v>
       </c>
       <c r="J139" s="29"/>
     </row>
-    <row r="140" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="47" t="s">
+    <row r="140" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="55" t="str">
+        <f t="shared" si="20"/>
+        <v>7414</v>
+      </c>
+      <c r="B140" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="C140" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D140" s="51">
+        <v>1001204447414</v>
+      </c>
+      <c r="E140" s="24"/>
+      <c r="F140" s="23">
+        <v>1</v>
+      </c>
+      <c r="G140" s="23">
+        <f>E140</f>
+        <v>0</v>
+      </c>
+      <c r="H140" s="14">
+        <v>8</v>
+      </c>
+      <c r="I140" s="14">
+        <v>60</v>
+      </c>
+      <c r="J140" s="29"/>
+    </row>
+    <row r="141" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B140" s="42" t="s">
+      <c r="B141" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="C140" s="42"/>
-      <c r="D140" s="42"/>
-      <c r="E140" s="24"/>
-      <c r="F140" s="41"/>
-      <c r="G140" s="42"/>
-      <c r="H140" s="42"/>
-      <c r="I140" s="42"/>
-      <c r="J140" s="43"/>
-    </row>
-    <row r="141" spans="1:10" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="55" t="str">
-        <f t="shared" ref="A141:A150" si="27">RIGHT(D141,4)</f>
+      <c r="C141" s="42"/>
+      <c r="D141" s="42"/>
+      <c r="E141" s="24"/>
+      <c r="F141" s="41"/>
+      <c r="G141" s="42"/>
+      <c r="H141" s="42"/>
+      <c r="I141" s="42"/>
+      <c r="J141" s="43"/>
+    </row>
+    <row r="142" spans="1:10" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="55" t="str">
+        <f t="shared" ref="A142:A151" si="27">RIGHT(D142,4)</f>
         <v>4584</v>
       </c>
-      <c r="B141" s="98" t="s">
+      <c r="B142" s="98" t="s">
         <v>125</v>
       </c>
-      <c r="C141" s="50" t="s">
+      <c r="C142" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D141" s="97">
+      <c r="D142" s="97">
         <v>1001092674584</v>
       </c>
-      <c r="E141" s="24"/>
-      <c r="F141" s="23">
+      <c r="E142" s="24"/>
+      <c r="F142" s="23">
         <v>2.5</v>
       </c>
-      <c r="G141" s="23">
-        <f>E141</f>
+      <c r="G142" s="23">
+        <f>E142</f>
         <v>0</v>
       </c>
-      <c r="H141" s="14">
+      <c r="H142" s="14">
         <v>7.5</v>
       </c>
-      <c r="I141" s="14">
+      <c r="I142" s="14">
         <v>60</v>
-      </c>
-      <c r="J141" s="29"/>
-    </row>
-    <row r="142" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="55" t="str">
-        <f t="shared" si="27"/>
-        <v>6495</v>
-      </c>
-      <c r="B142" s="98" t="s">
-        <v>97</v>
-      </c>
-      <c r="C142" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D142" s="51">
-        <v>1001092436495</v>
-      </c>
-      <c r="E142" s="24"/>
-      <c r="F142" s="56">
-        <v>0.3</v>
-      </c>
-      <c r="G142" s="23">
-        <f>E142*F142</f>
-        <v>0</v>
-      </c>
-      <c r="H142" s="29">
-        <v>1.8</v>
-      </c>
-      <c r="I142" s="29">
-        <v>45</v>
       </c>
       <c r="J142" s="29"/>
     </row>
     <row r="143" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>6470</v>
-      </c>
-      <c r="B143" s="95" t="s">
-        <v>126</v>
+        <v>6495</v>
+      </c>
+      <c r="B143" s="98" t="s">
+        <v>97</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D143" s="51">
-        <v>1001092436470</v>
+        <v>1001092436495</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="56">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G143" s="23">
-        <f t="shared" ref="G143:G144" si="28">E143</f>
+        <f>E143*F143</f>
         <v>0</v>
       </c>
       <c r="H143" s="29">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I143" s="29">
         <v>45</v>
@@ -9830,57 +9827,57 @@
     <row r="144" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>5452</v>
+        <v>6470</v>
       </c>
       <c r="B144" s="95" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="C144" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D144" s="51">
-        <v>1001092485452</v>
+        <v>1001092436470</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="56">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="G144" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="G144:G145" si="28">E144</f>
         <v>0</v>
       </c>
       <c r="H144" s="29">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="I144" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J144" s="29"/>
     </row>
     <row r="145" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>3215</v>
+        <v>5452</v>
       </c>
       <c r="B145" s="95" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D145" s="51">
-        <v>1001094053215</v>
+        <v>1001092485452</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="56">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G145" s="23">
-        <f>E145*F145</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H145" s="29">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I145" s="29">
         <v>60</v>
@@ -9890,57 +9887,57 @@
     <row r="146" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>6866</v>
+        <v>3215</v>
       </c>
       <c r="B146" s="95" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D146" s="51">
-        <v>1001095716866</v>
+        <v>1001094053215</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="56">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G146" s="23">
-        <f>E146</f>
+        <f>E146*F146</f>
         <v>0</v>
       </c>
       <c r="H146" s="29">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I146" s="29">
         <v>60</v>
       </c>
       <c r="J146" s="29"/>
     </row>
-    <row r="147" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>5495</v>
-      </c>
-      <c r="B147" s="53" t="s">
-        <v>96</v>
+        <v>6866</v>
+      </c>
+      <c r="B147" s="95" t="s">
+        <v>93</v>
       </c>
       <c r="C147" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D147" s="96">
-        <v>1001093345495</v>
+        <v>23</v>
+      </c>
+      <c r="D147" s="51">
+        <v>1001095716866</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="56">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G147" s="23">
-        <f t="shared" ref="G147:G149" si="29">E147*F147</f>
+        <f>E147</f>
         <v>0</v>
       </c>
       <c r="H147" s="29">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I147" s="29">
         <v>60</v>
@@ -9950,159 +9947,159 @@
     <row r="148" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>7377</v>
+        <v>5495</v>
       </c>
       <c r="B148" s="53" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C148" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D148" s="96">
-        <v>1001095027377</v>
+        <v>1001093345495</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="56">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G148" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="G148:G150" si="29">E148*F148</f>
         <v>0</v>
       </c>
       <c r="H148" s="29">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I148" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J148" s="29"/>
     </row>
     <row r="149" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>6925</v>
+        <v>7377</v>
       </c>
       <c r="B149" s="53" t="s">
-        <v>214</v>
+        <v>127</v>
       </c>
       <c r="C149" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D149" s="96">
-        <v>1001095226925</v>
+        <v>1001095027377</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="56">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G149" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H149" s="29">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I149" s="29">
         <v>45</v>
       </c>
       <c r="J149" s="29"/>
     </row>
-    <row r="150" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="55" t="str">
         <f t="shared" si="27"/>
-        <v>6025</v>
+        <v>6925</v>
       </c>
       <c r="B150" s="53" t="s">
-        <v>128</v>
+        <v>213</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D150" s="96">
-        <v>1001094966025</v>
+        <v>1001095226925</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="56">
+        <v>0.6</v>
+      </c>
+      <c r="G150" s="23">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H150" s="29">
+        <v>4.8</v>
+      </c>
+      <c r="I150" s="29">
+        <v>45</v>
+      </c>
+      <c r="J150" s="29"/>
+    </row>
+    <row r="151" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="55" t="str">
+        <f t="shared" si="27"/>
+        <v>6025</v>
+      </c>
+      <c r="B151" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C151" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D151" s="96">
+        <v>1001094966025</v>
+      </c>
+      <c r="E151" s="24"/>
+      <c r="F151" s="56">
         <v>3</v>
       </c>
-      <c r="G150" s="23">
-        <f>E150</f>
+      <c r="G151" s="23">
+        <f>E151</f>
         <v>0</v>
       </c>
-      <c r="H150" s="29">
+      <c r="H151" s="29">
         <v>6</v>
       </c>
-      <c r="I150" s="29">
+      <c r="I151" s="29">
         <v>60</v>
       </c>
-      <c r="J150" s="29"/>
-    </row>
-    <row r="151" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="47" t="s">
+      <c r="J151" s="29"/>
+    </row>
+    <row r="152" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="B151" s="42" t="s">
+      <c r="B152" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="C151" s="42"/>
-      <c r="D151" s="42"/>
-      <c r="E151" s="24"/>
-      <c r="F151" s="41"/>
-      <c r="G151" s="42"/>
-      <c r="H151" s="42"/>
-      <c r="I151" s="42"/>
-      <c r="J151" s="43"/>
-    </row>
-    <row r="152" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="55" t="str">
-        <f t="shared" ref="A152:A163" si="30">RIGHT(D152,4)</f>
+      <c r="C152" s="42"/>
+      <c r="D152" s="42"/>
+      <c r="E152" s="24"/>
+      <c r="F152" s="41"/>
+      <c r="G152" s="42"/>
+      <c r="H152" s="42"/>
+      <c r="I152" s="42"/>
+      <c r="J152" s="43"/>
+    </row>
+    <row r="153" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="55" t="str">
+        <f t="shared" ref="A153:A164" si="30">RIGHT(D153,4)</f>
         <v>7090</v>
       </c>
-      <c r="B152" s="35" t="s">
+      <c r="B153" s="35" t="s">
         <v>102</v>
-      </c>
-      <c r="C152" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D152" s="51">
-        <v>1001084217090</v>
-      </c>
-      <c r="E152" s="24"/>
-      <c r="F152" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G152" s="23">
-        <f t="shared" ref="G152:G153" si="31">E152*F152</f>
-        <v>0</v>
-      </c>
-      <c r="H152" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I152" s="14">
-        <v>50</v>
-      </c>
-      <c r="J152" s="29"/>
-    </row>
-    <row r="153" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="55" t="str">
-        <f t="shared" si="30"/>
-        <v>7187</v>
-      </c>
-      <c r="B153" s="35" t="s">
-        <v>103</v>
       </c>
       <c r="C153" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D153" s="51">
-        <v>1001085637187</v>
+        <v>1001084217090</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="23">
         <v>0.3</v>
       </c>
       <c r="G153" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="G153:G154" si="31">E153*F153</f>
         <v>0</v>
       </c>
       <c r="H153" s="14">
@@ -10116,111 +10113,111 @@
     <row r="154" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6620</v>
+        <v>7187</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D154" s="51">
-        <v>1001081596620</v>
+        <v>1001085637187</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G154" s="23">
-        <f>E154</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H154" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I154" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J154" s="29"/>
     </row>
     <row r="155" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6008</v>
+        <v>6620</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>223</v>
+        <v>99</v>
       </c>
       <c r="C155" s="50" t="s">
         <v>23</v>
       </c>
       <c r="D155" s="51">
-        <v>1001084856008</v>
+        <v>1001081596620</v>
       </c>
       <c r="E155" s="24"/>
-      <c r="F155" s="23"/>
+      <c r="F155" s="23">
+        <v>1.05</v>
+      </c>
       <c r="G155" s="23">
         <f>E155</f>
         <v>0</v>
       </c>
-      <c r="H155" s="14"/>
-      <c r="I155" s="14"/>
+      <c r="H155" s="14">
+        <v>3.15</v>
+      </c>
+      <c r="I155" s="14">
+        <v>30</v>
+      </c>
       <c r="J155" s="29"/>
     </row>
     <row r="156" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>7103</v>
+        <v>6008</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>104</v>
+        <v>222</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D156" s="51">
-        <v>1001223297103</v>
+        <v>1001084856008</v>
       </c>
       <c r="E156" s="24"/>
-      <c r="F156" s="23">
-        <v>0.18</v>
-      </c>
+      <c r="F156" s="23"/>
       <c r="G156" s="23">
-        <f t="shared" ref="G156:G163" si="32">E156*F156</f>
+        <f>E156</f>
         <v>0</v>
       </c>
-      <c r="H156" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I156" s="14">
-        <v>50</v>
-      </c>
+      <c r="H156" s="14"/>
+      <c r="I156" s="14"/>
       <c r="J156" s="29"/>
     </row>
     <row r="157" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="55" t="str">
-        <f>RIGHT(D157,4)</f>
-        <v>7092</v>
+        <f t="shared" si="30"/>
+        <v>7103</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C157" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D157" s="51">
-        <v>1001223297092</v>
+        <v>1001223297103</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G157" s="23">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="G157:G164" si="32">E157*F157</f>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I157" s="14">
         <v>50</v>
@@ -10229,58 +10226,58 @@
     </row>
     <row r="158" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="55" t="str">
-        <f t="shared" si="30"/>
-        <v>6228</v>
+        <f>RIGHT(D158,4)</f>
+        <v>7092</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D158" s="51">
-        <v>1001225416228</v>
+        <v>1001223297092</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G158" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H158" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I158" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J158" s="29"/>
     </row>
     <row r="159" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6448</v>
+        <v>6228</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D159" s="51">
-        <v>1001234146448</v>
+        <v>1001225416228</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G159" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H159" s="14">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I159" s="14">
         <v>45</v>
@@ -10290,27 +10287,27 @@
     <row r="160" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6208</v>
+        <v>6448</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C160" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D160" s="51">
-        <v>1001220226208</v>
+        <v>1001234146448</v>
       </c>
       <c r="E160" s="24"/>
       <c r="F160" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G160" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H160" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I160" s="14">
         <v>45</v>
@@ -10320,124 +10317,144 @@
     <row r="161" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6754</v>
+        <v>6208</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="C161" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D161" s="51">
-        <v>1001225406754</v>
+        <v>1001220226208</v>
       </c>
       <c r="E161" s="24"/>
       <c r="F161" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G161" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H161" s="14">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="I161" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J161" s="29"/>
     </row>
     <row r="162" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>6279</v>
+        <v>6754</v>
       </c>
       <c r="B162" s="35" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C162" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D162" s="51">
-        <v>1001220286279</v>
+        <v>1001225406754</v>
       </c>
       <c r="E162" s="24"/>
       <c r="F162" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G162" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H162" s="14">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="I162" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J162" s="29"/>
     </row>
-    <row r="163" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="55" t="str">
         <f t="shared" si="30"/>
-        <v>7288</v>
+        <v>6279</v>
       </c>
       <c r="B163" s="35" t="s">
-        <v>213</v>
+        <v>100</v>
       </c>
       <c r="C163" s="50" t="s">
         <v>21</v>
       </c>
       <c r="D163" s="51">
-        <v>1001223907288</v>
+        <v>1001220286279</v>
       </c>
       <c r="E163" s="24"/>
       <c r="F163" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G163" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H163" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I163" s="14">
+        <v>45</v>
+      </c>
+      <c r="J163" s="29"/>
+    </row>
+    <row r="164" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="55" t="str">
+        <f t="shared" si="30"/>
+        <v>7288</v>
+      </c>
+      <c r="B164" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="C164" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D164" s="51">
+        <v>1001223907288</v>
+      </c>
+      <c r="E164" s="24"/>
+      <c r="F164" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G164" s="23">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H164" s="14">
         <v>1</v>
       </c>
-      <c r="I163" s="14">
+      <c r="I164" s="14">
         <v>60</v>
       </c>
-      <c r="J163" s="29"/>
-    </row>
-    <row r="164" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="48"/>
-      <c r="B164" s="45" t="s">
+      <c r="J164" s="29"/>
+    </row>
+    <row r="165" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="48"/>
+      <c r="B165" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C164" s="16"/>
-      <c r="D164" s="36"/>
-      <c r="E164" s="17">
-        <f>SUM(E10:E163)</f>
+      <c r="C165" s="16"/>
+      <c r="D165" s="36"/>
+      <c r="E165" s="17">
+        <f>SUM(E10:E164)</f>
         <v>0</v>
       </c>
-      <c r="F164" s="17"/>
-      <c r="G164" s="17">
-        <f>SUM(G11:G163)</f>
+      <c r="F165" s="17"/>
+      <c r="G165" s="17">
+        <f>SUM(G11:G164)</f>
         <v>0</v>
       </c>
-      <c r="H164" s="17"/>
-      <c r="I164" s="17"/>
-      <c r="J164" s="17"/>
-    </row>
-    <row r="165" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="37"/>
-      <c r="C165" s="18"/>
-      <c r="D165" s="40"/>
-      <c r="F165" s="19"/>
-      <c r="G165" s="19"/>
-      <c r="H165" s="20"/>
-      <c r="I165" s="20"/>
-      <c r="J165" s="21"/>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H165" s="17"/>
+      <c r="I165" s="17"/>
+      <c r="J165" s="17"/>
+    </row>
+    <row r="166" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B166" s="37"/>
       <c r="C166" s="18"/>
       <c r="D166" s="40"/>
@@ -10510,21 +10527,21 @@
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
       <c r="C173" s="18"/>
-      <c r="D173" s="53"/>
-      <c r="E173" s="4"/>
-      <c r="F173" s="53"/>
-      <c r="G173" s="57"/>
-      <c r="H173" s="51"/>
+      <c r="D173" s="40"/>
+      <c r="F173" s="19"/>
+      <c r="G173" s="19"/>
+      <c r="H173" s="20"/>
       <c r="I173" s="20"/>
       <c r="J173" s="21"/>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B174" s="37"/>
       <c r="C174" s="18"/>
-      <c r="D174" s="40"/>
-      <c r="F174" s="19"/>
-      <c r="G174" s="19"/>
-      <c r="H174" s="20"/>
+      <c r="D174" s="53"/>
+      <c r="E174" s="4"/>
+      <c r="F174" s="53"/>
+      <c r="G174" s="57"/>
+      <c r="H174" s="51"/>
       <c r="I174" s="20"/>
       <c r="J174" s="21"/>
     </row>
@@ -25668,13 +25685,23 @@
       <c r="I1688" s="20"/>
       <c r="J1688" s="21"/>
     </row>
+    <row r="1689" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1689" s="37"/>
+      <c r="C1689" s="18"/>
+      <c r="D1689" s="40"/>
+      <c r="F1689" s="19"/>
+      <c r="G1689" s="19"/>
+      <c r="H1689" s="20"/>
+      <c r="I1689" s="20"/>
+      <c r="J1689" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J164" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J165" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D173">
+  <conditionalFormatting sqref="D174">
     <cfRule type="duplicateValues" dxfId="312" priority="1"/>
     <cfRule type="duplicateValues" dxfId="311" priority="2"/>
     <cfRule type="duplicateValues" dxfId="310" priority="3"/>
